--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="70">
   <si>
     <t>Výroba</t>
   </si>
@@ -54,19 +54,7 @@
     <t>Benzín / nafta</t>
   </si>
   <si>
-    <t>Stepanenko Solomiia</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
     <t>Suroviny</t>
-  </si>
-  <si>
-    <t>Paziak Viktoriia</t>
   </si>
   <si>
     <t>Ostatní</t>
@@ -79,6 +67,12 @@
   </si>
   <si>
     <t>Počet dní</t>
+  </si>
+  <si>
+    <t>Paziak Viktoriia</t>
+  </si>
+  <si>
+    <t>Stepanenko Solomiia</t>
   </si>
   <si>
     <t>Kursheva Diana</t>
@@ -1396,7 +1390,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46147.0</v>
+        <v>46154.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1415,8 +1409,8 @@
       <c r="D2" s="13"/>
       <c r="E2" s="14"/>
       <c r="F2" s="15">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(A14:A20) + SUM(FILTER(HR!W5:W48, HR!A5:A48 &lt;&gt; """")) + J13 + J15"),40068.0)</f>
-        <v>40068</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(A14:A20) + SUM(FILTER(HR!W5:W48, HR!A5:A48 &lt;&gt; """")) + J13 + J15"),40004.0)</f>
+        <v>40004</v>
       </c>
       <c r="H2" s="16"/>
       <c r="K2" s="16"/>
@@ -1563,25 +1557,19 @@
     <row r="14">
       <c r="A14" s="38">
         <f t="array" ref="A14">IF(ISBLANK(B14), 0, IF(ISNUMBER(MATCH(B14, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B14, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B14, HR!B:B, 0)) * (F14 * 24), 0)))</f>
-        <v>64</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="40" t="s">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
       <c r="E14" s="41"/>
       <c r="F14" s="42" t="str">
         <f t="shared" ref="F14:F20" si="1">IF(OR(ISBLANK(B14), ISBLANK(D14), D14=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))+1, TIMEVALUE(IF(ISBLANK(D14), "00:00", D14))) - TIMEVALUE(IF(ISBLANK(C14), "00:00", C14)) - TIMEVALUE(IF(ISBLANK(E14), "00:00", E14))), "hh:mm"))
 </f>
-        <v>08:00</v>
+        <v>0:00</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H14" s="44"/>
       <c r="I14" s="45"/>
@@ -1593,22 +1581,16 @@
         <f t="array" ref="A15">IF(ISBLANK(B15), 0, IF(ISNUMBER(MATCH(B15, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B15, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B15, HR!B:B, 0)) * (F15 * 24), 0)))</f>
         <v>0</v>
       </c>
-      <c r="B15" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="40" t="s">
-        <v>14</v>
-      </c>
+      <c r="B15" s="47"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
       <c r="E15" s="40"/>
       <c r="F15" s="42" t="str">
         <f t="shared" si="1"/>
-        <v>08:00</v>
+        <v>0:00</v>
       </c>
       <c r="G15" s="48" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H15" s="49"/>
       <c r="I15" s="50"/>
@@ -1758,13 +1740,13 @@
         <v>Výroba</v>
       </c>
       <c r="C1" s="62">
-        <v>46082.0</v>
+        <v>46113.0</v>
       </c>
       <c r="D1" s="63" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E1" s="62">
-        <v>46112.0</v>
+        <v>46142.0</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>2</v>
@@ -1780,7 +1762,7 @@
       <c r="D2" s="12"/>
       <c r="E2" s="13"/>
       <c r="F2" s="65">
-        <v>1275695.5</v>
+        <v>1224118.75</v>
       </c>
       <c r="H2" s="16"/>
     </row>
@@ -1788,12 +1770,12 @@
       <c r="A3" s="66"/>
       <c r="B3" s="67" t="str">
         <f>CHOOSE(WEEKDAY(C1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Neděle</v>
+        <v>Středa</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="67" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Úterý</v>
+        <v>Čtvrtek</v>
       </c>
       <c r="E3" s="5"/>
       <c r="H3" s="16"/>
@@ -1811,7 +1793,7 @@
     <row r="5">
       <c r="A5" s="68"/>
       <c r="B5" s="69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1851,7 +1833,7 @@
       <c r="D7" s="19"/>
       <c r="E7" s="14"/>
       <c r="F7" s="74" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7" s="44"/>
       <c r="H7" s="45"/>
@@ -1869,7 +1851,7 @@
       <c r="D8" s="8"/>
       <c r="E8" s="76"/>
       <c r="F8" s="77" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G8" s="49"/>
       <c r="H8" s="50"/>
@@ -1884,7 +1866,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="79" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D9" s="79" t="s">
         <v>10</v>
@@ -1894,61 +1876,61 @@
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="71"/>
       <c r="B10" s="80" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C10" s="81">
-        <v>31.0</v>
+        <v>22.0</v>
       </c>
       <c r="D10" s="82">
-        <v>163.0</v>
+        <v>176.0</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="71"/>
       <c r="B11" s="80" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" s="81">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="D11" s="82">
-        <v>176.0</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="71"/>
       <c r="B12" s="80" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C12" s="81">
-        <v>20.0</v>
+        <v>14.0</v>
       </c>
       <c r="D12" s="82">
-        <v>151.0</v>
+        <v>112.0</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="71"/>
       <c r="B13" s="80" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C13" s="81">
         <v>13.0</v>
       </c>
       <c r="D13" s="83">
-        <v>134.0</v>
+        <v>111.0</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71"/>
       <c r="B14" s="80" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" s="81">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="D14" s="83">
-        <v>6.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
@@ -2156,10 +2138,10 @@
     </row>
     <row r="4">
       <c r="A4" s="88" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -2256,8 +2238,8 @@
       <c r="T5" s="84"/>
       <c r="U5" s="84"/>
       <c r="V5" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
+        <v>57</v>
       </c>
       <c r="W5" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2322,8 +2304,8 @@
       <c r="T6" s="84"/>
       <c r="U6" s="84"/>
       <c r="V6" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),68.5)</f>
+        <v>68.5</v>
       </c>
       <c r="W6" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2382,8 +2364,8 @@
       <c r="T7" s="84"/>
       <c r="U7" s="84"/>
       <c r="V7" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
+        <v>40</v>
       </c>
       <c r="W7" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2451,8 +2433,8 @@
       <c r="T8" s="84"/>
       <c r="U8" s="84"/>
       <c r="V8" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.5)</f>
-        <v>8.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.5)</f>
+        <v>51.5</v>
       </c>
       <c r="W8" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2514,8 +2496,8 @@
       <c r="T9" s="84"/>
       <c r="U9" s="84"/>
       <c r="V9" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),61.5)</f>
+        <v>61.5</v>
       </c>
       <c r="W9" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2583,8 +2565,8 @@
       <c r="T10" s="84"/>
       <c r="U10" s="84"/>
       <c r="V10" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
+        <v>56</v>
       </c>
       <c r="W10" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2643,12 +2625,12 @@
       <c r="T11" s="84"/>
       <c r="U11" s="84"/>
       <c r="V11" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
+        <v>38</v>
       </c>
       <c r="W11" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1367.548)</f>
-        <v>1367.548</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7423.832)</f>
+        <v>7423.832</v>
       </c>
       <c r="X11" s="84"/>
       <c r="Y11" s="84"/>
@@ -2763,8 +2745,8 @@
       <c r="T13" s="84"/>
       <c r="U13" s="84"/>
       <c r="V13" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.5)</f>
-        <v>8.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
       </c>
       <c r="W13" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2826,12 +2808,12 @@
       <c r="T14" s="84"/>
       <c r="U14" s="84"/>
       <c r="V14" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
+        <v>12</v>
       </c>
       <c r="W14" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1983.696)</f>
+        <v>1983.696</v>
       </c>
       <c r="X14" s="84"/>
       <c r="Y14" s="84"/>
@@ -2889,8 +2871,8 @@
       <c r="T15" s="84"/>
       <c r="U15" s="84"/>
       <c r="V15" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
+        <v>57</v>
       </c>
       <c r="W15" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2952,8 +2934,8 @@
       <c r="T16" s="84"/>
       <c r="U16" s="84"/>
       <c r="V16" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69.0)</f>
+        <v>69</v>
       </c>
       <c r="W16" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -3012,12 +2994,12 @@
       <c r="T17" s="84"/>
       <c r="U17" s="84"/>
       <c r="V17" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.5)</f>
-        <v>6.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.5)</f>
+        <v>21.5</v>
       </c>
       <c r="W17" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1149.2)</f>
-        <v>1149.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3801.2)</f>
+        <v>3801.2</v>
       </c>
       <c r="X17" s="84"/>
       <c r="Y17" s="84"/>
@@ -3072,12 +3054,12 @@
       <c r="T18" s="84"/>
       <c r="U18" s="84"/>
       <c r="V18" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
       </c>
       <c r="W18" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1513.408)</f>
-        <v>1513.408</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9269.624)</f>
+        <v>9269.624</v>
       </c>
       <c r="X18" s="84"/>
       <c r="Y18" s="84"/>
@@ -3132,12 +3114,12 @@
       <c r="T19" s="84"/>
       <c r="U19" s="84"/>
       <c r="V19" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
       </c>
       <c r="W19" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1352.52)</f>
+        <v>1352.52</v>
       </c>
       <c r="X19" s="84"/>
       <c r="Y19" s="84"/>
@@ -3192,12 +3174,12 @@
       <c r="T20" s="84"/>
       <c r="U20" s="84"/>
       <c r="V20" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.5)</f>
-        <v>9.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.5)</f>
+        <v>33.5</v>
       </c>
       <c r="W20" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1679.6)</f>
-        <v>1679.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5922.8)</f>
+        <v>5922.8</v>
       </c>
       <c r="X20" s="84"/>
       <c r="Y20" s="84"/>
@@ -3258,8 +3240,8 @@
       <c r="T21" s="84"/>
       <c r="U21" s="84"/>
       <c r="V21" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.0)</f>
+        <v>51</v>
       </c>
       <c r="W21" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3318,8 +3300,8 @@
       <c r="T22" s="84"/>
       <c r="U22" s="84"/>
       <c r="V22" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
-        <v>17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.5)</f>
+        <v>126.5</v>
       </c>
       <c r="W22" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3378,12 +3360,12 @@
       <c r="T23" s="84"/>
       <c r="U23" s="84"/>
       <c r="V23" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
+        <v>52</v>
       </c>
       <c r="W23" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1818.388)</f>
-        <v>1818.388</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8596.016)</f>
+        <v>8596.016</v>
       </c>
       <c r="X23" s="84"/>
       <c r="Y23" s="84"/>
@@ -3441,12 +3423,12 @@
       <c r="T24" s="84"/>
       <c r="U24" s="84"/>
       <c r="V24" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.5)</f>
-        <v>10.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
+        <v>55</v>
       </c>
       <c r="W24" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1856.4)</f>
-        <v>1856.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9724.0)</f>
+        <v>9724</v>
       </c>
       <c r="X24" s="84"/>
       <c r="Y24" s="84"/>
@@ -3501,12 +3483,12 @@
       <c r="T25" s="84"/>
       <c r="U25" s="84"/>
       <c r="V25" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
+        <v>16</v>
       </c>
       <c r="W25" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2446.912)</f>
+        <v>2446.912</v>
       </c>
       <c r="X25" s="84"/>
       <c r="Y25" s="84"/>
@@ -3615,12 +3597,12 @@
       <c r="T27" s="84"/>
       <c r="U27" s="84"/>
       <c r="V27" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
+        <v>34</v>
       </c>
       <c r="W27" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6431.984)</f>
+        <v>6431.984</v>
       </c>
       <c r="X27" s="84"/>
       <c r="Y27" s="84"/>
@@ -3681,12 +3663,12 @@
       <c r="T28" s="84"/>
       <c r="U28" s="84"/>
       <c r="V28" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.0)</f>
+        <v>59</v>
       </c>
       <c r="W28" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10431.2)</f>
+        <v>10431.2</v>
       </c>
       <c r="X28" s="84"/>
       <c r="Y28" s="84"/>
@@ -3801,12 +3783,12 @@
       <c r="T30" s="84"/>
       <c r="U30" s="84"/>
       <c r="V30" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
       </c>
       <c r="W30" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1983.696)</f>
-        <v>1983.696</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10910.328)</f>
+        <v>10910.328</v>
       </c>
       <c r="X30" s="84"/>
       <c r="Y30" s="84"/>
@@ -3864,12 +3846,12 @@
       <c r="T31" s="84"/>
       <c r="U31" s="84"/>
       <c r="V31" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.0)</f>
+        <v>44</v>
       </c>
       <c r="W31" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),917.592)</f>
-        <v>917.592</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6729.008)</f>
+        <v>6729.008</v>
       </c>
       <c r="X31" s="84"/>
       <c r="Y31" s="84"/>
@@ -4107,12 +4089,12 @@
       <c r="T35" s="84"/>
       <c r="U35" s="84"/>
       <c r="V35" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
+        <v>33</v>
       </c>
       <c r="W35" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1322.464)</f>
-        <v>1322.464</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5455.164)</f>
+        <v>5455.164</v>
       </c>
       <c r="X35" s="84"/>
       <c r="Y35" s="84"/>
@@ -4167,12 +4149,12 @@
       <c r="T36" s="84"/>
       <c r="U36" s="84"/>
       <c r="V36" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
+        <v>25</v>
       </c>
       <c r="W36" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4132.7)</f>
+        <v>4132.7</v>
       </c>
       <c r="X36" s="84"/>
       <c r="Y36" s="84"/>
@@ -4227,12 +4209,12 @@
       <c r="T37" s="84"/>
       <c r="U37" s="84"/>
       <c r="V37" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.5)</f>
-        <v>10.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.5)</f>
+        <v>21.5</v>
       </c>
       <c r="W37" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1735.734)</f>
-        <v>1735.734</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3554.122)</f>
+        <v>3554.122</v>
       </c>
       <c r="X37" s="84"/>
       <c r="Y37" s="84"/>
@@ -4290,12 +4272,12 @@
       <c r="T38" s="84"/>
       <c r="U38" s="84"/>
       <c r="V38" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
+        <v>52</v>
       </c>
       <c r="W38" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8596.016)</f>
+        <v>8596.016</v>
       </c>
       <c r="X38" s="84"/>
       <c r="Y38" s="84"/>
@@ -4359,12 +4341,12 @@
       <c r="T39" s="84"/>
       <c r="U39" s="84"/>
       <c r="V39" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
+        <v>56</v>
       </c>
       <c r="W39" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9257.248)</f>
+        <v>9257.248</v>
       </c>
       <c r="X39" s="84"/>
       <c r="Y39" s="84"/>
@@ -4479,12 +4461,12 @@
       <c r="T41" s="84"/>
       <c r="U41" s="84"/>
       <c r="V41" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.0)</f>
+        <v>58</v>
       </c>
       <c r="W41" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1487.772)</f>
-        <v>1487.772</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9587.864)</f>
+        <v>9587.864</v>
       </c>
       <c r="X41" s="84"/>
       <c r="Y41" s="84"/>
@@ -4514,14 +4496,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kuzníková Nicol")</f>
-        <v>Kuzníková Nicol</v>
-      </c>
-      <c r="E42" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="D42" s="84"/>
+      <c r="E42" s="84"/>
       <c r="F42" s="84"/>
       <c r="G42" s="84"/>
       <c r="H42" s="84"/>
@@ -5406,12 +5382,12 @@
       <c r="T60" s="84"/>
       <c r="U60" s="84"/>
       <c r="V60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),184.0)</f>
-        <v>184</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1435.5)</f>
+        <v>1435.5</v>
       </c>
       <c r="W60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),594858.282)</f>
-        <v>594858.282</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),703632.7139999998)</f>
+        <v>703632.714</v>
       </c>
       <c r="X60" s="84"/>
       <c r="Y60" s="84"/>
@@ -6093,12 +6069,12 @@
       <c r="T75" s="84"/>
       <c r="U75" s="84"/>
       <c r="V75" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
+        <v>34</v>
       </c>
       <c r="W75" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5100.0)</f>
+        <v>5100</v>
       </c>
       <c r="X75" s="84"/>
       <c r="Y75" s="84"/>
@@ -6150,12 +6126,12 @@
       <c r="T76" s="84"/>
       <c r="U76" s="84"/>
       <c r="V76" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
+        <v>39</v>
       </c>
       <c r="W76" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6895.2)</f>
+        <v>6895.2</v>
       </c>
       <c r="X76" s="84"/>
       <c r="Y76" s="84"/>
@@ -6264,12 +6240,12 @@
       <c r="T78" s="84"/>
       <c r="U78" s="84"/>
       <c r="V78" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
       <c r="W78" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1768.0)</f>
+        <v>1768</v>
       </c>
       <c r="X78" s="84"/>
       <c r="Y78" s="84"/>
@@ -6327,12 +6303,12 @@
       <c r="T79" s="84"/>
       <c r="U79" s="84"/>
       <c r="V79" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
+        <v>7</v>
       </c>
       <c r="W79" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1070.524)</f>
+        <v>1070.524</v>
       </c>
       <c r="X79" s="84"/>
       <c r="Y79" s="84"/>
@@ -6390,12 +6366,12 @@
       <c r="T80" s="84"/>
       <c r="U80" s="84"/>
       <c r="V80" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
+        <v>17</v>
       </c>
       <c r="W80" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2810.236)</f>
+        <v>2810.236</v>
       </c>
       <c r="X80" s="84"/>
       <c r="Y80" s="84"/>
@@ -6430,7 +6406,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
         <v>Zličín</v>
       </c>
-      <c r="F81" s="84"/>
+      <c r="F81" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G81" s="84"/>
       <c r="H81" s="84"/>
       <c r="I81" s="84"/>
@@ -6447,12 +6426,12 @@
       <c r="T81" s="84"/>
       <c r="U81" s="84"/>
       <c r="V81" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.5)</f>
+        <v>50.5</v>
       </c>
       <c r="W81" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7723.066)</f>
+        <v>7723.066</v>
       </c>
       <c r="X81" s="84"/>
       <c r="Y81" s="84"/>
@@ -6561,12 +6540,12 @@
       <c r="T83" s="84"/>
       <c r="U83" s="84"/>
       <c r="V83" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
+        <v>14</v>
       </c>
       <c r="W83" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2141.048)</f>
+        <v>2141.048</v>
       </c>
       <c r="X83" s="84"/>
       <c r="Y83" s="84"/>
@@ -6621,12 +6600,12 @@
       <c r="T84" s="84"/>
       <c r="U84" s="84"/>
       <c r="V84" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
+        <v>12</v>
       </c>
       <c r="W84" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1983.696)</f>
+        <v>1983.696</v>
       </c>
       <c r="X84" s="84"/>
       <c r="Y84" s="84"/>
@@ -6678,12 +6657,12 @@
       <c r="T85" s="84"/>
       <c r="U85" s="84"/>
       <c r="V85" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
+        <v>16</v>
       </c>
       <c r="W85" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2400.0)</f>
+        <v>2400</v>
       </c>
       <c r="X85" s="84"/>
       <c r="Y85" s="84"/>
@@ -6792,12 +6771,12 @@
       <c r="T87" s="84"/>
       <c r="U87" s="84"/>
       <c r="V87" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="W87" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),764.66)</f>
+        <v>764.66</v>
       </c>
       <c r="X87" s="84"/>
       <c r="Y87" s="84"/>
@@ -6915,12 +6894,12 @@
       <c r="T89" s="84"/>
       <c r="U89" s="84"/>
       <c r="V89" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
+        <v>22</v>
       </c>
       <c r="W89" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1360.0)</f>
-        <v>1360</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3740.0)</f>
+        <v>3740</v>
       </c>
       <c r="X89" s="84"/>
       <c r="Y89" s="84"/>
@@ -6975,12 +6954,12 @@
       <c r="T90" s="84"/>
       <c r="U90" s="84"/>
       <c r="V90" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),61.0)</f>
+        <v>61</v>
       </c>
       <c r="W90" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1600.0)</f>
-        <v>1600</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9760.0)</f>
+        <v>9760</v>
       </c>
       <c r="X90" s="84"/>
       <c r="Y90" s="84"/>
@@ -7058,14 +7037,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D92" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Killiakov Andrei")</f>
-        <v>Killiakov Andrei</v>
-      </c>
-      <c r="E92" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="D92" s="84"/>
+      <c r="E92" s="84"/>
       <c r="F92" s="84"/>
       <c r="G92" s="84"/>
       <c r="H92" s="84"/>
@@ -7146,12 +7119,12 @@
       <c r="T93" s="84"/>
       <c r="U93" s="84"/>
       <c r="V93" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="W93" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1653.08)</f>
-        <v>1653.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13389.948)</f>
+        <v>13389.948</v>
       </c>
       <c r="X93" s="84"/>
       <c r="Y93" s="84"/>
@@ -7209,12 +7182,12 @@
       <c r="T94" s="84"/>
       <c r="U94" s="84"/>
       <c r="V94" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
-        <v>14</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
+        <v>63</v>
       </c>
       <c r="W94" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2314.312)</f>
-        <v>2314.312</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10414.404)</f>
+        <v>10414.404</v>
       </c>
       <c r="X94" s="84"/>
       <c r="Y94" s="84"/>
@@ -7326,8 +7299,8 @@
       <c r="T96" s="84"/>
       <c r="U96" s="84"/>
       <c r="V96" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.0)</f>
+        <v>45</v>
       </c>
       <c r="W96" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44995.2)</f>
@@ -7383,12 +7356,12 @@
       <c r="T97" s="84"/>
       <c r="U97" s="84"/>
       <c r="V97" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
+        <v>24</v>
       </c>
       <c r="W97" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3967.392)</f>
+        <v>3967.392</v>
       </c>
       <c r="X97" s="84"/>
       <c r="Y97" s="84"/>
@@ -7449,12 +7422,12 @@
       <c r="T98" s="84"/>
       <c r="U98" s="84"/>
       <c r="V98" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
       </c>
       <c r="W98" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),848.64)</f>
+        <v>848.64</v>
       </c>
       <c r="X98" s="84"/>
       <c r="Y98" s="84"/>
@@ -7506,12 +7479,12 @@
       <c r="T99" s="84"/>
       <c r="U99" s="84"/>
       <c r="V99" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
+        <v>17</v>
       </c>
       <c r="W99" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1272.96)</f>
-        <v>1272.96</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2404.48)</f>
+        <v>2404.48</v>
       </c>
       <c r="X99" s="84"/>
       <c r="Y99" s="84"/>
@@ -7839,12 +7812,12 @@
       <c r="T105" s="84"/>
       <c r="U105" s="84"/>
       <c r="V105" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
+        <v>37</v>
       </c>
       <c r="W105" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1529.32)</f>
-        <v>1529.32</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5658.484)</f>
+        <v>5658.484</v>
       </c>
       <c r="X105" s="84"/>
       <c r="Y105" s="84"/>
@@ -7947,12 +7920,12 @@
       <c r="T107" s="84"/>
       <c r="U107" s="84"/>
       <c r="V107" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62.0)</f>
+        <v>62</v>
       </c>
       <c r="W107" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8680.0)</f>
+        <v>8680</v>
       </c>
       <c r="X107" s="84"/>
       <c r="Y107" s="84"/>
@@ -8007,12 +7980,12 @@
       <c r="T108" s="84"/>
       <c r="U108" s="84"/>
       <c r="V108" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.5)</f>
+        <v>42.5</v>
       </c>
       <c r="W108" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),743.886)</f>
-        <v>743.886</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7025.59)</f>
+        <v>7025.59</v>
       </c>
       <c r="X108" s="84"/>
       <c r="Y108" s="84"/>
@@ -8064,12 +8037,12 @@
       <c r="T109" s="84"/>
       <c r="U109" s="84"/>
       <c r="V109" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
       </c>
       <c r="W109" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2905.708)</f>
+        <v>2905.708</v>
       </c>
       <c r="X109" s="84"/>
       <c r="Y109" s="84"/>
@@ -8121,12 +8094,12 @@
       <c r="T110" s="84"/>
       <c r="U110" s="84"/>
       <c r="V110" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.0)</f>
+        <v>45</v>
       </c>
       <c r="W110" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),764.66)</f>
-        <v>764.66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6364.8)</f>
+        <v>6364.8</v>
       </c>
       <c r="X110" s="84"/>
       <c r="Y110" s="84"/>
@@ -8235,12 +8208,12 @@
       <c r="T112" s="84"/>
       <c r="U112" s="84"/>
       <c r="V112" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="W112" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),636.48)</f>
+        <v>636.48</v>
       </c>
       <c r="X112" s="84"/>
       <c r="Y112" s="84"/>
@@ -8292,12 +8265,12 @@
       <c r="T113" s="84"/>
       <c r="U113" s="84"/>
       <c r="V113" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
       </c>
       <c r="W113" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),848.64)</f>
+        <v>848.64</v>
       </c>
       <c r="X113" s="84"/>
       <c r="Y113" s="84"/>
@@ -8409,12 +8382,12 @@
       <c r="T115" s="84"/>
       <c r="U115" s="84"/>
       <c r="V115" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.5)</f>
+        <v>24.5</v>
       </c>
       <c r="W115" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),826.54)</f>
-        <v>826.54</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4050.0460000000003)</f>
+        <v>4050.046</v>
       </c>
       <c r="X115" s="84"/>
       <c r="Y115" s="84"/>
@@ -8466,12 +8439,12 @@
       <c r="T116" s="84"/>
       <c r="U116" s="84"/>
       <c r="V116" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.5)</f>
+        <v>5.5</v>
       </c>
       <c r="W116" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),841.126)</f>
+        <v>841.126</v>
       </c>
       <c r="X116" s="84"/>
       <c r="Y116" s="84"/>
@@ -8523,12 +8496,12 @@
       <c r="T117" s="84"/>
       <c r="U117" s="84"/>
       <c r="V117" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.5)</f>
-        <v>8.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.5)</f>
+        <v>64.5</v>
       </c>
       <c r="W117" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1405.118)</f>
-        <v>1405.118</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10662.366)</f>
+        <v>10662.366</v>
       </c>
       <c r="X117" s="84"/>
       <c r="Y117" s="84"/>
@@ -8631,12 +8604,12 @@
       <c r="T119" s="84"/>
       <c r="U119" s="84"/>
       <c r="V119" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
+        <v>25</v>
       </c>
       <c r="W119" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3536.0)</f>
+        <v>3536</v>
       </c>
       <c r="X119" s="84"/>
       <c r="Y119" s="84"/>
@@ -8688,12 +8661,12 @@
       <c r="T120" s="84"/>
       <c r="U120" s="84"/>
       <c r="V120" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
+        <v>18</v>
       </c>
       <c r="W120" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),707.2)</f>
-        <v>707.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2545.92)</f>
+        <v>2545.92</v>
       </c>
       <c r="X120" s="84"/>
       <c r="Y120" s="84"/>
@@ -8720,10 +8693,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D121" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Přibyl Jan")</f>
-        <v>Přibyl Jan</v>
-      </c>
+      <c r="D121" s="84"/>
       <c r="E121" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
         <v>Chodov</v>
@@ -8834,14 +8804,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D123" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Hrach Michal")</f>
-        <v>Hrach Michal</v>
-      </c>
-      <c r="E123" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
+      <c r="D123" s="84"/>
+      <c r="E123" s="84"/>
       <c r="F123" s="84"/>
       <c r="G123" s="84"/>
       <c r="H123" s="84"/>
@@ -8891,14 +8855,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D124" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kvapil Filip Leon")</f>
-        <v>Kvapil Filip Leon</v>
-      </c>
-      <c r="E124" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
-      </c>
+      <c r="D124" s="84"/>
+      <c r="E124" s="84"/>
       <c r="F124" s="84"/>
       <c r="G124" s="84"/>
       <c r="H124" s="84"/>
@@ -8973,12 +8931,12 @@
       <c r="T125" s="84"/>
       <c r="U125" s="84"/>
       <c r="V125" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
       </c>
       <c r="W125" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2905.708)</f>
+        <v>2905.708</v>
       </c>
       <c r="X125" s="84"/>
       <c r="Y125" s="84"/>
@@ -9005,14 +8963,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D126" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Irena Kovacsova")</f>
-        <v>Irena Kovacsova</v>
-      </c>
-      <c r="E126" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bolevec")</f>
-        <v>Bolevec</v>
-      </c>
+      <c r="D126" s="84"/>
+      <c r="E126" s="84"/>
       <c r="F126" s="84"/>
       <c r="G126" s="84"/>
       <c r="H126" s="84"/>
@@ -12519,12 +12471,12 @@
       <c r="T196" s="84"/>
       <c r="U196" s="84"/>
       <c r="V196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.0)</f>
-        <v>96</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),903.0)</f>
+        <v>903</v>
       </c>
       <c r="W196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89970.79999999999)</f>
-        <v>89970.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209635.88600000003)</f>
+        <v>209635.886</v>
       </c>
       <c r="X196" s="84"/>
       <c r="Y196" s="84"/>
@@ -43914,7 +43866,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C1" s="94" t="s">
         <v>4</v>
@@ -43926,22 +43878,22 @@
         <v>8</v>
       </c>
       <c r="F1" s="94" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G1" s="94" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="94" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I1" s="94" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J1" s="94" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K1" s="94" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -43949,22 +43901,22 @@
         <v>45528.0</v>
       </c>
       <c r="B2" s="94" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="E2" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="96" t="s">
+      <c r="F2" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="96" t="s">
+      <c r="G2" s="96" t="s">
         <v>33</v>
-      </c>
-      <c r="F2" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="96" t="s">
-        <v>35</v>
       </c>
       <c r="H2" s="97">
         <v>3728.0</v>
@@ -43975,22 +43927,22 @@
         <v>45528.0</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" s="94" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D3" s="96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E3" s="96" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F3" s="96" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G3" s="96" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H3" s="97">
         <v>3728.0</v>
@@ -44001,19 +43953,19 @@
         <v>45528.0</v>
       </c>
       <c r="B4" s="94" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" s="96" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E4" s="96" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="96" t="s">
         <v>36</v>
-      </c>
-      <c r="G4" s="96" t="s">
-        <v>38</v>
       </c>
       <c r="H4" s="97">
         <v>3728.0</v>
@@ -44024,7 +43976,7 @@
         <v>45528.0</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I5" s="97">
         <v>12.0</v>
@@ -44041,22 +43993,22 @@
         <v>45526.0</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="96" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="96" t="s">
+      <c r="F6" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="96" t="s">
+      <c r="G6" s="96" t="s">
         <v>33</v>
-      </c>
-      <c r="F6" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="96" t="s">
-        <v>35</v>
       </c>
       <c r="H6" s="97">
         <v>3728.0</v>
@@ -44067,22 +44019,22 @@
         <v>45526.0</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C7" s="94" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D7" s="96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E7" s="96" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F7" s="96" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G7" s="96" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H7" s="97">
         <v>3728.0</v>
@@ -44093,19 +44045,19 @@
         <v>45526.0</v>
       </c>
       <c r="B8" s="94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C8" s="94" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D8" s="96" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E8" s="96" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="96" t="s">
         <v>36</v>
-      </c>
-      <c r="G8" s="96" t="s">
-        <v>38</v>
       </c>
       <c r="H8" s="97">
         <v>3728.0</v>
@@ -44116,7 +44068,7 @@
         <v>45526.0</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I9" s="97">
         <v>12.0</v>
@@ -44133,22 +44085,22 @@
         <v>45526.0</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="96" t="s">
+      <c r="F10" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="96" t="s">
+      <c r="G10" s="96" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="96" t="s">
-        <v>35</v>
       </c>
       <c r="H10" s="97">
         <v>3728.0</v>
@@ -44159,22 +44111,22 @@
         <v>45526.0</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="94" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D11" s="96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E11" s="96" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F11" s="96" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G11" s="96" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H11" s="97">
         <v>3728.0</v>
@@ -44185,19 +44137,19 @@
         <v>45526.0</v>
       </c>
       <c r="B12" s="94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="94" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="96" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E12" s="96" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="96" t="s">
         <v>36</v>
-      </c>
-      <c r="G12" s="96" t="s">
-        <v>38</v>
       </c>
       <c r="H12" s="97">
         <v>3728.0</v>
@@ -44208,7 +44160,7 @@
         <v>45526.0</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I13" s="97">
         <v>12.0</v>
@@ -44225,7 +44177,7 @@
         <v>45532.0</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -44233,7 +44185,7 @@
         <v>45533.0</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
@@ -44241,7 +44193,7 @@
         <v>45534.0</v>
       </c>
       <c r="B16" s="94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -44249,7 +44201,7 @@
         <v>45535.0</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -44283,7 +44235,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="98" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -44487,7 +44439,7 @@
       <c r="Y19" s="100"/>
       <c r="Z19" s="100"/>
       <c r="AA19" s="94" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AB19" s="94">
         <v>-11.0</v>
@@ -44812,7 +44764,7 @@
       <c r="Y30" s="100"/>
       <c r="Z30" s="100"/>
       <c r="AA30" s="94" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB30" s="94">
         <v>-8.0</v>
@@ -44933,7 +44885,7 @@
       <c r="Y34" s="100"/>
       <c r="Z34" s="100"/>
       <c r="AA34" s="94" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AB34" s="94">
         <v>0.0</v>
@@ -45052,7 +45004,7 @@
       <c r="Y38" s="100"/>
       <c r="Z38" s="100"/>
       <c r="AA38" s="94" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB38" s="94">
         <v>-12.0</v>
@@ -45086,7 +45038,7 @@
       <c r="Y39" s="100"/>
       <c r="Z39" s="100"/>
       <c r="AA39" s="94" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AB39" s="94">
         <v>0.0</v>
@@ -45178,7 +45130,7 @@
       <c r="Y42" s="100"/>
       <c r="Z42" s="100"/>
       <c r="AA42" s="94" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB42" s="94">
         <v>6.0</v>
@@ -45357,7 +45309,7 @@
       <c r="Y48" s="100"/>
       <c r="Z48" s="100"/>
       <c r="AA48" s="94" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AB48" s="94">
         <v>-13.0</v>
@@ -45478,7 +45430,7 @@
       <c r="Y52" s="100"/>
       <c r="Z52" s="100"/>
       <c r="AA52" s="94" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB52" s="94">
         <v>5.0</v>
@@ -45686,7 +45638,7 @@
       <c r="Y59" s="100"/>
       <c r="Z59" s="100"/>
       <c r="AA59" s="94" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AB59" s="94">
         <v>-9.0</v>
@@ -45807,7 +45759,7 @@
       <c r="Y63" s="100"/>
       <c r="Z63" s="100"/>
       <c r="AA63" s="94" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AB63" s="94">
         <v>-19.0</v>
@@ -46015,7 +45967,7 @@
       <c r="Y70" s="100"/>
       <c r="Z70" s="100"/>
       <c r="AA70" s="94" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AB70" s="94">
         <v>-14.0</v>
@@ -46484,7 +46436,7 @@
       <c r="Y86" s="100"/>
       <c r="Z86" s="100"/>
       <c r="AA86" s="94" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AB86" s="94">
         <v>-21.0</v>
@@ -46518,7 +46470,7 @@
       <c r="Y87" s="100"/>
       <c r="Z87" s="100"/>
       <c r="AA87" s="94" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AB87" s="94">
         <v>-7.0</v>
@@ -46552,7 +46504,7 @@
       <c r="Y88" s="100"/>
       <c r="Z88" s="100"/>
       <c r="AA88" s="94" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AB88" s="94">
         <v>-10.0</v>
@@ -46586,7 +46538,7 @@
       <c r="Y89" s="100"/>
       <c r="Z89" s="100"/>
       <c r="AA89" s="94" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AB89" s="94">
         <v>-6.0</v>
@@ -46679,7 +46631,7 @@
       <c r="Y92" s="100"/>
       <c r="Z92" s="100"/>
       <c r="AA92" s="94" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AB92" s="94">
         <v>-17.0</v>
@@ -46945,7 +46897,7 @@
       <c r="Y101" s="100"/>
       <c r="Z101" s="100"/>
       <c r="AA101" s="94" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AB101" s="94">
         <v>-6.0</v>
@@ -46979,7 +46931,7 @@
       <c r="Y102" s="100"/>
       <c r="Z102" s="100"/>
       <c r="AA102" s="94" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AB102" s="94">
         <v>1.0</v>
@@ -47071,7 +47023,7 @@
       <c r="Y105" s="100"/>
       <c r="Z105" s="100"/>
       <c r="AA105" s="94" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AB105" s="94">
         <v>-2.0</v>
@@ -47134,7 +47086,7 @@
       <c r="Y107" s="100"/>
       <c r="Z107" s="100"/>
       <c r="AA107" s="94" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AB107" s="94">
         <v>-12.0</v>
@@ -47226,7 +47178,7 @@
       <c r="Y110" s="100"/>
       <c r="Z110" s="100"/>
       <c r="AA110" s="94" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AB110" s="94">
         <v>-14.0</v>
@@ -47260,7 +47212,7 @@
       <c r="Y111" s="100"/>
       <c r="Z111" s="100"/>
       <c r="AA111" s="94" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AB111" s="94">
         <v>-6.0</v>
@@ -47294,7 +47246,7 @@
       <c r="Y112" s="100"/>
       <c r="Z112" s="100"/>
       <c r="AA112" s="94" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AB112" s="94">
         <v>-11.0</v>
@@ -47357,7 +47309,7 @@
       <c r="Y114" s="100"/>
       <c r="Z114" s="100"/>
       <c r="AA114" s="94" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AB114" s="94">
         <v>-1.0</v>
@@ -47449,7 +47401,7 @@
       <c r="Y117" s="100"/>
       <c r="Z117" s="100"/>
       <c r="AA117" s="94" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AB117" s="94">
         <v>12.0</v>
@@ -47512,7 +47464,7 @@
       <c r="Y119" s="100"/>
       <c r="Z119" s="100"/>
       <c r="AA119" s="94" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AB119" s="94">
         <v>-17.0</v>
@@ -47633,7 +47585,7 @@
       <c r="Y123" s="100"/>
       <c r="Z123" s="100"/>
       <c r="AA123" s="94" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AB123" s="94">
         <v>-15.0</v>
@@ -47784,7 +47736,7 @@
       <c r="Y128" s="100"/>
       <c r="Z128" s="100"/>
       <c r="AA128" s="94" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AB128" s="94">
         <v>-11.0</v>
@@ -48169,7 +48121,7 @@
       <c r="Y141" s="100"/>
       <c r="Z141" s="100"/>
       <c r="AA141" s="94" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AB141" s="94">
         <v>-10.0</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="68">
   <si>
     <t>Výroba</t>
   </si>
@@ -69,19 +69,7 @@
     <t>Počet dní</t>
   </si>
   <si>
-    <t>Paziak Viktoriia</t>
-  </si>
-  <si>
-    <t>Stepanenko Solomiia</t>
-  </si>
-  <si>
-    <t>Kursheva Diana</t>
-  </si>
-  <si>
-    <t>Hřebík Martin</t>
-  </si>
-  <si>
-    <t>Chlubna Tomáš</t>
+    <t>Lažek Jaroslav</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -120,10 +108,16 @@
     <t>01:00</t>
   </si>
   <si>
+    <t>Stepanenko Solomiia</t>
+  </si>
+  <si>
     <t>10:00</t>
   </si>
   <si>
     <t>11:00</t>
+  </si>
+  <si>
+    <t>Hřebík Martin</t>
   </si>
   <si>
     <t>05:00</t>
@@ -1390,7 +1384,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46154.0</v>
+        <v>46162.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1419,7 +1413,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Úterý</v>
+        <v>Středa</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1710,7 +1704,7 @@
   </conditionalFormatting>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="B14:B20">
-      <formula1>"Sova Martin,Paziak Viktoriia,Stepanenko Solomiia,Kursheva Diana,Chlubna Tomáš,Hřebík Martin"</formula1>
+      <formula1>"Sova Martin,Paziak Viktoriia,Stepanenko Solomiia,Kursheva Diana,Lažek Jaroslav,Chlubna Tomáš,Hřebík Martin"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
@@ -1740,13 +1734,13 @@
         <v>Výroba</v>
       </c>
       <c r="C1" s="62">
-        <v>46113.0</v>
+        <v>46151.0</v>
       </c>
       <c r="D1" s="63" t="s">
         <v>14</v>
       </c>
       <c r="E1" s="62">
-        <v>46142.0</v>
+        <v>46151.0</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>2</v>
@@ -1762,7 +1756,7 @@
       <c r="D2" s="12"/>
       <c r="E2" s="13"/>
       <c r="F2" s="65">
-        <v>1224118.75</v>
+        <v>0.0</v>
       </c>
       <c r="H2" s="16"/>
     </row>
@@ -1770,12 +1764,12 @@
       <c r="A3" s="66"/>
       <c r="B3" s="67" t="str">
         <f>CHOOSE(WEEKDAY(C1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Středa</v>
+        <v>Sobota</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="67" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Čtvrtek</v>
+        <v>Sobota</v>
       </c>
       <c r="E3" s="5"/>
       <c r="H3" s="16"/>
@@ -1879,59 +1873,35 @@
         <v>17</v>
       </c>
       <c r="C10" s="81">
-        <v>22.0</v>
+        <v>1.0</v>
       </c>
       <c r="D10" s="82">
-        <v>176.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="71"/>
-      <c r="B11" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="81">
-        <v>19.0</v>
-      </c>
-      <c r="D11" s="82">
-        <v>151.0</v>
-      </c>
+      <c r="B11" s="80"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="82"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="71"/>
-      <c r="B12" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="81">
-        <v>14.0</v>
-      </c>
-      <c r="D12" s="82">
-        <v>112.0</v>
-      </c>
+      <c r="B12" s="80"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="82"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="71"/>
-      <c r="B13" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="81">
-        <v>13.0</v>
-      </c>
-      <c r="D13" s="83">
-        <v>111.0</v>
-      </c>
+      <c r="B13" s="80"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="83"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71"/>
-      <c r="B14" s="80" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="81">
-        <v>4.0</v>
-      </c>
-      <c r="D14" s="83">
-        <v>21.0</v>
-      </c>
+      <c r="B14" s="80"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="83"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="71"/>
@@ -2138,10 +2108,10 @@
     </row>
     <row r="4">
       <c r="A4" s="88" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C4" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -2238,8 +2208,8 @@
       <c r="T5" s="84"/>
       <c r="U5" s="84"/>
       <c r="V5" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
-        <v>57</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.5)</f>
+        <v>111.5</v>
       </c>
       <c r="W5" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2304,8 +2274,8 @@
       <c r="T6" s="84"/>
       <c r="U6" s="84"/>
       <c r="V6" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),68.5)</f>
-        <v>68.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.0)</f>
+        <v>114</v>
       </c>
       <c r="W6" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2412,8 +2382,8 @@
         <v>Malešice</v>
       </c>
       <c r="G8" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
       </c>
       <c r="H8" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
@@ -2433,8 +2403,8 @@
       <c r="T8" s="84"/>
       <c r="U8" s="84"/>
       <c r="V8" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.5)</f>
-        <v>51.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
+        <v>108</v>
       </c>
       <c r="W8" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2496,8 +2466,8 @@
       <c r="T9" s="84"/>
       <c r="U9" s="84"/>
       <c r="V9" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),61.5)</f>
-        <v>61.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),99.5)</f>
+        <v>99.5</v>
       </c>
       <c r="W9" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2565,8 +2535,8 @@
       <c r="T10" s="84"/>
       <c r="U10" s="84"/>
       <c r="V10" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
-        <v>56</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.5)</f>
+        <v>64.5</v>
       </c>
       <c r="W10" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2625,12 +2595,12 @@
       <c r="T11" s="84"/>
       <c r="U11" s="84"/>
       <c r="V11" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
-        <v>38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
+        <v>70</v>
       </c>
       <c r="W11" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7423.832)</f>
-        <v>7423.832</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13675.48)</f>
+        <v>13675.48</v>
       </c>
       <c r="X11" s="84"/>
       <c r="Y11" s="84"/>
@@ -2792,7 +2762,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="G14" s="84"/>
+      <c r="G14" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
       <c r="H14" s="84"/>
       <c r="I14" s="84"/>
       <c r="J14" s="84"/>
@@ -2808,12 +2781,12 @@
       <c r="T14" s="84"/>
       <c r="U14" s="84"/>
       <c r="V14" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
+        <v>20</v>
       </c>
       <c r="W14" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1983.696)</f>
-        <v>1983.696</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3306.16)</f>
+        <v>3306.16</v>
       </c>
       <c r="X14" s="84"/>
       <c r="Y14" s="84"/>
@@ -2871,8 +2844,8 @@
       <c r="T15" s="84"/>
       <c r="U15" s="84"/>
       <c r="V15" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),57.0)</f>
-        <v>57</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102.0)</f>
+        <v>102</v>
       </c>
       <c r="W15" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2934,8 +2907,8 @@
       <c r="T16" s="84"/>
       <c r="U16" s="84"/>
       <c r="V16" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69.0)</f>
-        <v>69</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.0)</f>
+        <v>133</v>
       </c>
       <c r="W16" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2994,12 +2967,12 @@
       <c r="T17" s="84"/>
       <c r="U17" s="84"/>
       <c r="V17" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.5)</f>
-        <v>21.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.5)</f>
+        <v>22.5</v>
       </c>
       <c r="W17" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3801.2)</f>
-        <v>3801.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3978.0)</f>
+        <v>3978</v>
       </c>
       <c r="X17" s="84"/>
       <c r="Y17" s="84"/>
@@ -3054,12 +3027,12 @@
       <c r="T18" s="84"/>
       <c r="U18" s="84"/>
       <c r="V18" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
-        <v>49</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="W18" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9269.624)</f>
-        <v>9269.624</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16392.688000000002)</f>
+        <v>16392.688</v>
       </c>
       <c r="X18" s="84"/>
       <c r="Y18" s="84"/>
@@ -3114,12 +3087,12 @@
       <c r="T19" s="84"/>
       <c r="U19" s="84"/>
       <c r="V19" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.5)</f>
+        <v>66.5</v>
       </c>
       <c r="W19" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1352.52)</f>
-        <v>1352.52</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14990.43)</f>
+        <v>14990.43</v>
       </c>
       <c r="X19" s="84"/>
       <c r="Y19" s="84"/>
@@ -3174,12 +3147,12 @@
       <c r="T20" s="84"/>
       <c r="U20" s="84"/>
       <c r="V20" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.5)</f>
-        <v>33.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.5)</f>
+        <v>54.5</v>
       </c>
       <c r="W20" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5922.8)</f>
-        <v>5922.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9635.6)</f>
+        <v>9635.6</v>
       </c>
       <c r="X20" s="84"/>
       <c r="Y20" s="84"/>
@@ -3240,8 +3213,8 @@
       <c r="T21" s="84"/>
       <c r="U21" s="84"/>
       <c r="V21" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.0)</f>
-        <v>51</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
+        <v>100</v>
       </c>
       <c r="W21" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3300,8 +3273,8 @@
       <c r="T22" s="84"/>
       <c r="U22" s="84"/>
       <c r="V22" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.5)</f>
-        <v>126.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.5)</f>
+        <v>174.5</v>
       </c>
       <c r="W22" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3423,12 +3396,12 @@
       <c r="T24" s="84"/>
       <c r="U24" s="84"/>
       <c r="V24" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
-        <v>55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
+        <v>105</v>
       </c>
       <c r="W24" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9724.0)</f>
-        <v>9724</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17984.0)</f>
+        <v>17984</v>
       </c>
       <c r="X24" s="84"/>
       <c r="Y24" s="84"/>
@@ -3483,12 +3456,12 @@
       <c r="T25" s="84"/>
       <c r="U25" s="84"/>
       <c r="V25" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
-        <v>16</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
+        <v>27</v>
       </c>
       <c r="W25" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2446.912)</f>
-        <v>2446.912</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4129.164)</f>
+        <v>4129.164</v>
       </c>
       <c r="X25" s="84"/>
       <c r="Y25" s="84"/>
@@ -3597,12 +3570,12 @@
       <c r="T27" s="84"/>
       <c r="U27" s="84"/>
       <c r="V27" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
-        <v>34</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.5)</f>
+        <v>47.5</v>
       </c>
       <c r="W27" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6431.984)</f>
-        <v>6431.984</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8985.86)</f>
+        <v>8985.86</v>
       </c>
       <c r="X27" s="84"/>
       <c r="Y27" s="84"/>
@@ -3663,12 +3636,12 @@
       <c r="T28" s="84"/>
       <c r="U28" s="84"/>
       <c r="V28" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.0)</f>
-        <v>59</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102.0)</f>
+        <v>102</v>
       </c>
       <c r="W28" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10431.2)</f>
-        <v>10431.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17543.6)</f>
+        <v>17543.6</v>
       </c>
       <c r="X28" s="84"/>
       <c r="Y28" s="84"/>
@@ -3783,12 +3756,12 @@
       <c r="T30" s="84"/>
       <c r="U30" s="84"/>
       <c r="V30" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
-        <v>66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.5)</f>
+        <v>103.5</v>
       </c>
       <c r="W30" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10910.328)</f>
-        <v>10910.328</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16776.203)</f>
+        <v>16776.203</v>
       </c>
       <c r="X30" s="84"/>
       <c r="Y30" s="84"/>
@@ -3830,7 +3803,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="G31" s="84"/>
+      <c r="G31" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
       <c r="H31" s="84"/>
       <c r="I31" s="84"/>
       <c r="J31" s="84"/>
@@ -3846,12 +3822,12 @@
       <c r="T31" s="84"/>
       <c r="U31" s="84"/>
       <c r="V31" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.0)</f>
-        <v>44</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.0)</f>
+        <v>78</v>
       </c>
       <c r="W31" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6729.008)</f>
-        <v>6729.008</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11928.696)</f>
+        <v>11928.696</v>
       </c>
       <c r="X31" s="84"/>
       <c r="Y31" s="84"/>
@@ -4089,12 +4065,12 @@
       <c r="T35" s="84"/>
       <c r="U35" s="84"/>
       <c r="V35" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
-        <v>33</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),72.0)</f>
+        <v>72</v>
       </c>
       <c r="W35" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5455.164)</f>
-        <v>5455.164</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11902.176)</f>
+        <v>11902.176</v>
       </c>
       <c r="X35" s="84"/>
       <c r="Y35" s="84"/>
@@ -4272,12 +4248,12 @@
       <c r="T38" s="84"/>
       <c r="U38" s="84"/>
       <c r="V38" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
-        <v>52</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.5)</f>
+        <v>90.5</v>
       </c>
       <c r="W38" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8596.016)</f>
-        <v>8596.016</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14960.374)</f>
+        <v>14960.374</v>
       </c>
       <c r="X38" s="84"/>
       <c r="Y38" s="84"/>
@@ -4341,12 +4317,12 @@
       <c r="T39" s="84"/>
       <c r="U39" s="84"/>
       <c r="V39" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
-        <v>56</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.5)</f>
+        <v>106.5</v>
       </c>
       <c r="W39" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9257.248)</f>
-        <v>9257.248</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17187.977)</f>
+        <v>17187.977</v>
       </c>
       <c r="X39" s="84"/>
       <c r="Y39" s="84"/>
@@ -4461,12 +4437,12 @@
       <c r="T41" s="84"/>
       <c r="U41" s="84"/>
       <c r="V41" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.0)</f>
-        <v>58</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),99.0)</f>
+        <v>99</v>
       </c>
       <c r="W41" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9587.864)</f>
-        <v>9587.864</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16158.542)</f>
+        <v>16158.542</v>
       </c>
       <c r="X41" s="84"/>
       <c r="Y41" s="84"/>
@@ -5382,12 +5358,12 @@
       <c r="T60" s="84"/>
       <c r="U60" s="84"/>
       <c r="V60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1435.5)</f>
-        <v>1435.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2364.0)</f>
+        <v>2364</v>
       </c>
       <c r="W60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),703632.7139999998)</f>
-        <v>703632.714</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),793844.2679999996)</f>
+        <v>793844.268</v>
       </c>
       <c r="X60" s="84"/>
       <c r="Y60" s="84"/>
@@ -6069,12 +6045,12 @@
       <c r="T75" s="84"/>
       <c r="U75" s="84"/>
       <c r="V75" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
-        <v>34</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.0)</f>
+        <v>59</v>
       </c>
       <c r="W75" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5100.0)</f>
-        <v>5100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8850.0)</f>
+        <v>8850</v>
       </c>
       <c r="X75" s="84"/>
       <c r="Y75" s="84"/>
@@ -6126,12 +6102,12 @@
       <c r="T76" s="84"/>
       <c r="U76" s="84"/>
       <c r="V76" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
-        <v>39</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
+        <v>63</v>
       </c>
       <c r="W76" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6895.2)</f>
-        <v>6895.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11138.4)</f>
+        <v>11138.4</v>
       </c>
       <c r="X76" s="84"/>
       <c r="Y76" s="84"/>
@@ -6240,12 +6216,12 @@
       <c r="T78" s="84"/>
       <c r="U78" s="84"/>
       <c r="V78" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
+        <v>25</v>
       </c>
       <c r="W78" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1768.0)</f>
-        <v>1768</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4420.0)</f>
+        <v>4420</v>
       </c>
       <c r="X78" s="84"/>
       <c r="Y78" s="84"/>
@@ -6303,12 +6279,12 @@
       <c r="T79" s="84"/>
       <c r="U79" s="84"/>
       <c r="V79" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
+        <v>18</v>
       </c>
       <c r="W79" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1070.524)</f>
-        <v>1070.524</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2752.776)</f>
+        <v>2752.776</v>
       </c>
       <c r="X79" s="84"/>
       <c r="Y79" s="84"/>
@@ -6366,12 +6342,12 @@
       <c r="T80" s="84"/>
       <c r="U80" s="84"/>
       <c r="V80" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
-        <v>17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.5)</f>
+        <v>55.5</v>
       </c>
       <c r="W80" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2810.236)</f>
-        <v>2810.236</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9174.594000000001)</f>
+        <v>9174.594</v>
       </c>
       <c r="X80" s="84"/>
       <c r="Y80" s="84"/>
@@ -6426,12 +6402,12 @@
       <c r="T81" s="84"/>
       <c r="U81" s="84"/>
       <c r="V81" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.5)</f>
-        <v>50.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.5)</f>
+        <v>96.5</v>
       </c>
       <c r="W81" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7723.066)</f>
-        <v>7723.066</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14757.938)</f>
+        <v>14757.938</v>
       </c>
       <c r="X81" s="84"/>
       <c r="Y81" s="84"/>
@@ -6540,12 +6516,12 @@
       <c r="T83" s="84"/>
       <c r="U83" s="84"/>
       <c r="V83" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
-        <v>14</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
+        <v>24</v>
       </c>
       <c r="W83" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2141.048)</f>
-        <v>2141.048</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3670.368)</f>
+        <v>3670.368</v>
       </c>
       <c r="X83" s="84"/>
       <c r="Y83" s="84"/>
@@ -6600,12 +6576,12 @@
       <c r="T84" s="84"/>
       <c r="U84" s="84"/>
       <c r="V84" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
+        <v>33</v>
       </c>
       <c r="W84" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1983.696)</f>
-        <v>1983.696</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5455.164)</f>
+        <v>5455.164</v>
       </c>
       <c r="X84" s="84"/>
       <c r="Y84" s="84"/>
@@ -6657,12 +6633,12 @@
       <c r="T85" s="84"/>
       <c r="U85" s="84"/>
       <c r="V85" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
-        <v>16</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
+        <v>27</v>
       </c>
       <c r="W85" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2400.0)</f>
-        <v>2400</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4050.0)</f>
+        <v>4050</v>
       </c>
       <c r="X85" s="84"/>
       <c r="Y85" s="84"/>
@@ -6771,12 +6747,12 @@
       <c r="T87" s="84"/>
       <c r="U87" s="84"/>
       <c r="V87" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
       <c r="W87" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),764.66)</f>
-        <v>764.66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1529.32)</f>
+        <v>1529.32</v>
       </c>
       <c r="X87" s="84"/>
       <c r="Y87" s="84"/>
@@ -6857,7 +6833,7 @@
       <c r="A89" s="84"/>
       <c r="B89" s="89" t="str">
         <f>IF(OR(E89=Report!$B$1, F89=Report!$B$1, G89=Report!$B$1, H89=Report!$B$1), D89, "")</f>
-        <v/>
+        <v>Lažek Jaroslav</v>
       </c>
       <c r="C89" s="84" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -6879,7 +6855,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="H89" s="84"/>
+      <c r="H89" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
+        <v>Výroba</v>
+      </c>
       <c r="I89" s="84"/>
       <c r="J89" s="84"/>
       <c r="K89" s="84"/>
@@ -6894,12 +6873,12 @@
       <c r="T89" s="84"/>
       <c r="U89" s="84"/>
       <c r="V89" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
-        <v>22</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
+        <v>42</v>
       </c>
       <c r="W89" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3740.0)</f>
-        <v>3740</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7140.0)</f>
+        <v>7140</v>
       </c>
       <c r="X89" s="84"/>
       <c r="Y89" s="84"/>
@@ -6954,12 +6933,12 @@
       <c r="T90" s="84"/>
       <c r="U90" s="84"/>
       <c r="V90" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),61.0)</f>
-        <v>61</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
       </c>
       <c r="W90" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9760.0)</f>
-        <v>9760</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11840.0)</f>
+        <v>11840</v>
       </c>
       <c r="X90" s="84"/>
       <c r="Y90" s="84"/>
@@ -7119,12 +7098,12 @@
       <c r="T93" s="84"/>
       <c r="U93" s="84"/>
       <c r="V93" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.5)</f>
+        <v>133.5</v>
       </c>
       <c r="W93" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13389.948)</f>
-        <v>13389.948</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20893.943)</f>
+        <v>20893.943</v>
       </c>
       <c r="X93" s="84"/>
       <c r="Y93" s="84"/>
@@ -7182,12 +7161,12 @@
       <c r="T94" s="84"/>
       <c r="U94" s="84"/>
       <c r="V94" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
-        <v>63</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),120.0)</f>
+        <v>120</v>
       </c>
       <c r="W94" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10414.404)</f>
-        <v>10414.404</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19040.96)</f>
+        <v>19040.96</v>
       </c>
       <c r="X94" s="84"/>
       <c r="Y94" s="84"/>
@@ -7299,8 +7278,8 @@
       <c r="T96" s="84"/>
       <c r="U96" s="84"/>
       <c r="V96" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.0)</f>
-        <v>45</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.0)</f>
+        <v>65</v>
       </c>
       <c r="W96" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44995.2)</f>
@@ -7356,12 +7335,12 @@
       <c r="T97" s="84"/>
       <c r="U97" s="84"/>
       <c r="V97" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
-        <v>24</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
+        <v>38</v>
       </c>
       <c r="W97" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3967.392)</f>
-        <v>3967.392</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6281.704)</f>
+        <v>6281.704</v>
       </c>
       <c r="X97" s="84"/>
       <c r="Y97" s="84"/>
@@ -7422,12 +7401,12 @@
       <c r="T98" s="84"/>
       <c r="U98" s="84"/>
       <c r="V98" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
+        <v>12</v>
       </c>
       <c r="W98" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),848.64)</f>
-        <v>848.64</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1697.28)</f>
+        <v>1697.28</v>
       </c>
       <c r="X98" s="84"/>
       <c r="Y98" s="84"/>
@@ -7479,12 +7458,12 @@
       <c r="T99" s="84"/>
       <c r="U99" s="84"/>
       <c r="V99" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
-        <v>17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
+        <v>34</v>
       </c>
       <c r="W99" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2404.48)</f>
-        <v>2404.48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4808.96)</f>
+        <v>4808.96</v>
       </c>
       <c r="X99" s="84"/>
       <c r="Y99" s="84"/>
@@ -7812,12 +7791,12 @@
       <c r="T105" s="84"/>
       <c r="U105" s="84"/>
       <c r="V105" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
-        <v>37</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.5)</f>
+        <v>55.5</v>
       </c>
       <c r="W105" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5658.484)</f>
-        <v>5658.484</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8487.726)</f>
+        <v>8487.726</v>
       </c>
       <c r="X105" s="84"/>
       <c r="Y105" s="84"/>
@@ -7920,12 +7899,12 @@
       <c r="T107" s="84"/>
       <c r="U107" s="84"/>
       <c r="V107" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),62.0)</f>
-        <v>62</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.5)</f>
+        <v>113.5</v>
       </c>
       <c r="W107" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8680.0)</f>
-        <v>8680</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15890.0)</f>
+        <v>15890</v>
       </c>
       <c r="X107" s="84"/>
       <c r="Y107" s="84"/>
@@ -7980,12 +7959,12 @@
       <c r="T108" s="84"/>
       <c r="U108" s="84"/>
       <c r="V108" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.5)</f>
-        <v>42.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.5)</f>
+        <v>64.5</v>
       </c>
       <c r="W108" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7025.59)</f>
-        <v>7025.59</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10662.366)</f>
+        <v>10662.366</v>
       </c>
       <c r="X108" s="84"/>
       <c r="Y108" s="84"/>
@@ -8094,12 +8073,12 @@
       <c r="T110" s="84"/>
       <c r="U110" s="84"/>
       <c r="V110" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.0)</f>
-        <v>45</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),60.0)</f>
+        <v>60</v>
       </c>
       <c r="W110" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6364.8)</f>
-        <v>6364.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8486.4)</f>
+        <v>8486.4</v>
       </c>
       <c r="X110" s="84"/>
       <c r="Y110" s="84"/>
@@ -8151,12 +8130,12 @@
       <c r="T111" s="84"/>
       <c r="U111" s="84"/>
       <c r="V111" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
+        <v>15</v>
       </c>
       <c r="W111" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2293.98)</f>
+        <v>2293.98</v>
       </c>
       <c r="X111" s="84"/>
       <c r="Y111" s="84"/>
@@ -8208,12 +8187,12 @@
       <c r="T112" s="84"/>
       <c r="U112" s="84"/>
       <c r="V112" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.5)</f>
+        <v>8.5</v>
       </c>
       <c r="W112" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),636.48)</f>
-        <v>636.48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1202.24)</f>
+        <v>1202.24</v>
       </c>
       <c r="X112" s="84"/>
       <c r="Y112" s="84"/>
@@ -8265,12 +8244,12 @@
       <c r="T113" s="84"/>
       <c r="U113" s="84"/>
       <c r="V113" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
+        <v>24</v>
       </c>
       <c r="W113" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),848.64)</f>
-        <v>848.64</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3394.56)</f>
+        <v>3394.56</v>
       </c>
       <c r="X113" s="84"/>
       <c r="Y113" s="84"/>
@@ -8382,12 +8361,12 @@
       <c r="T115" s="84"/>
       <c r="U115" s="84"/>
       <c r="V115" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.5)</f>
-        <v>24.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.5)</f>
+        <v>31.5</v>
       </c>
       <c r="W115" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4050.0460000000003)</f>
-        <v>4050.046</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5207.202)</f>
+        <v>5207.202</v>
       </c>
       <c r="X115" s="84"/>
       <c r="Y115" s="84"/>
@@ -8439,12 +8418,12 @@
       <c r="T116" s="84"/>
       <c r="U116" s="84"/>
       <c r="V116" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.5)</f>
-        <v>5.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.5)</f>
+        <v>16.5</v>
       </c>
       <c r="W116" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),841.126)</f>
-        <v>841.126</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2523.378)</f>
+        <v>2523.378</v>
       </c>
       <c r="X116" s="84"/>
       <c r="Y116" s="84"/>
@@ -8496,12 +8475,12 @@
       <c r="T117" s="84"/>
       <c r="U117" s="84"/>
       <c r="V117" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.5)</f>
-        <v>64.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),123.0)</f>
+        <v>123</v>
       </c>
       <c r="W117" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10662.366)</f>
-        <v>10662.366</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19452.733999999997)</f>
+        <v>19452.734</v>
       </c>
       <c r="X117" s="84"/>
       <c r="Y117" s="84"/>
@@ -8931,12 +8910,12 @@
       <c r="T125" s="84"/>
       <c r="U125" s="84"/>
       <c r="V125" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
+        <v>35</v>
       </c>
       <c r="W125" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2905.708)</f>
-        <v>2905.708</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5352.62)</f>
+        <v>5352.62</v>
       </c>
       <c r="X125" s="84"/>
       <c r="Y125" s="84"/>
@@ -8963,8 +8942,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D126" s="84"/>
-      <c r="E126" s="84"/>
+      <c r="D126" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pavel Břicháč")</f>
+        <v>Pavel Břicháč</v>
+      </c>
+      <c r="E126" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F126" s="84"/>
       <c r="G126" s="84"/>
       <c r="H126" s="84"/>
@@ -8982,12 +8967,12 @@
       <c r="T126" s="84"/>
       <c r="U126" s="84"/>
       <c r="V126" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.5)</f>
+        <v>29.5</v>
       </c>
       <c r="W126" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4511.494)</f>
+        <v>4511.494</v>
       </c>
       <c r="X126" s="84"/>
       <c r="Y126" s="84"/>
@@ -12471,12 +12456,12 @@
       <c r="T196" s="84"/>
       <c r="U196" s="84"/>
       <c r="V196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),903.0)</f>
-        <v>903</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1575.0)</f>
+        <v>1575</v>
       </c>
       <c r="W196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),209635.88600000003)</f>
-        <v>209635.886</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309747.45900000003)</f>
+        <v>309747.459</v>
       </c>
       <c r="X196" s="84"/>
       <c r="Y196" s="84"/>
@@ -43866,7 +43851,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C1" s="94" t="s">
         <v>4</v>
@@ -43878,16 +43863,16 @@
         <v>8</v>
       </c>
       <c r="F1" s="94" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G1" s="94" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="94" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I1" s="94" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J1" s="94" t="s">
         <v>12</v>
@@ -43901,22 +43886,22 @@
         <v>45528.0</v>
       </c>
       <c r="B2" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="94" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="96" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="96" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="G2" s="96" t="s">
         <v>29</v>
-      </c>
-      <c r="D2" s="96" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="96" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="96" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="96" t="s">
-        <v>33</v>
       </c>
       <c r="H2" s="97">
         <v>3728.0</v>
@@ -43927,22 +43912,22 @@
         <v>45528.0</v>
       </c>
       <c r="B3" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="94" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="94" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="96" t="s">
-        <v>32</v>
-      </c>
       <c r="G3" s="96" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H3" s="97">
         <v>3728.0</v>
@@ -43953,19 +43938,19 @@
         <v>45528.0</v>
       </c>
       <c r="B4" s="94" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D4" s="96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E4" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="96" t="s">
         <v>34</v>
-      </c>
-      <c r="G4" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H4" s="97">
         <v>3728.0</v>
@@ -43976,7 +43961,7 @@
         <v>45528.0</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I5" s="97">
         <v>12.0</v>
@@ -43993,22 +43978,22 @@
         <v>45526.0</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" s="94" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="96" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="96" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="96" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="96" t="s">
         <v>29</v>
-      </c>
-      <c r="D6" s="96" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="96" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="96" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="96" t="s">
-        <v>33</v>
       </c>
       <c r="H6" s="97">
         <v>3728.0</v>
@@ -44019,22 +44004,22 @@
         <v>45526.0</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C7" s="94" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D7" s="96" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E7" s="96" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F7" s="96" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G7" s="96" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H7" s="97">
         <v>3728.0</v>
@@ -44045,19 +44030,19 @@
         <v>45526.0</v>
       </c>
       <c r="B8" s="94" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C8" s="94" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D8" s="96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E8" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="96" t="s">
         <v>34</v>
-      </c>
-      <c r="G8" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H8" s="97">
         <v>3728.0</v>
@@ -44068,7 +44053,7 @@
         <v>45526.0</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I9" s="97">
         <v>12.0</v>
@@ -44085,22 +44070,22 @@
         <v>45526.0</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10" s="94" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="96" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="96" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="96" t="s">
         <v>29</v>
-      </c>
-      <c r="D10" s="96" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="96" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="96" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="96" t="s">
-        <v>33</v>
       </c>
       <c r="H10" s="97">
         <v>3728.0</v>
@@ -44111,22 +44096,22 @@
         <v>45526.0</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C11" s="94" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D11" s="96" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E11" s="96" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F11" s="96" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G11" s="96" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H11" s="97">
         <v>3728.0</v>
@@ -44137,19 +44122,19 @@
         <v>45526.0</v>
       </c>
       <c r="B12" s="94" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C12" s="94" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D12" s="96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E12" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="96" t="s">
         <v>34</v>
-      </c>
-      <c r="G12" s="96" t="s">
-        <v>36</v>
       </c>
       <c r="H12" s="97">
         <v>3728.0</v>
@@ -44160,7 +44145,7 @@
         <v>45526.0</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I13" s="97">
         <v>12.0</v>
@@ -44177,7 +44162,7 @@
         <v>45532.0</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -44185,7 +44170,7 @@
         <v>45533.0</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -44193,7 +44178,7 @@
         <v>45534.0</v>
       </c>
       <c r="B16" s="94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -44201,7 +44186,7 @@
         <v>45535.0</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -44235,7 +44220,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="98" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -44439,7 +44424,7 @@
       <c r="Y19" s="100"/>
       <c r="Z19" s="100"/>
       <c r="AA19" s="94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AB19" s="94">
         <v>-11.0</v>
@@ -44764,7 +44749,7 @@
       <c r="Y30" s="100"/>
       <c r="Z30" s="100"/>
       <c r="AA30" s="94" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB30" s="94">
         <v>-8.0</v>
@@ -44885,7 +44870,7 @@
       <c r="Y34" s="100"/>
       <c r="Z34" s="100"/>
       <c r="AA34" s="94" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AB34" s="94">
         <v>0.0</v>
@@ -45004,7 +44989,7 @@
       <c r="Y38" s="100"/>
       <c r="Z38" s="100"/>
       <c r="AA38" s="94" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB38" s="94">
         <v>-12.0</v>
@@ -45038,7 +45023,7 @@
       <c r="Y39" s="100"/>
       <c r="Z39" s="100"/>
       <c r="AA39" s="94" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AB39" s="94">
         <v>0.0</v>
@@ -45130,7 +45115,7 @@
       <c r="Y42" s="100"/>
       <c r="Z42" s="100"/>
       <c r="AA42" s="94" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB42" s="94">
         <v>6.0</v>
@@ -45309,7 +45294,7 @@
       <c r="Y48" s="100"/>
       <c r="Z48" s="100"/>
       <c r="AA48" s="94" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AB48" s="94">
         <v>-13.0</v>
@@ -45430,7 +45415,7 @@
       <c r="Y52" s="100"/>
       <c r="Z52" s="100"/>
       <c r="AA52" s="94" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB52" s="94">
         <v>5.0</v>
@@ -45638,7 +45623,7 @@
       <c r="Y59" s="100"/>
       <c r="Z59" s="100"/>
       <c r="AA59" s="94" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AB59" s="94">
         <v>-9.0</v>
@@ -45759,7 +45744,7 @@
       <c r="Y63" s="100"/>
       <c r="Z63" s="100"/>
       <c r="AA63" s="94" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB63" s="94">
         <v>-19.0</v>
@@ -45967,7 +45952,7 @@
       <c r="Y70" s="100"/>
       <c r="Z70" s="100"/>
       <c r="AA70" s="94" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AB70" s="94">
         <v>-14.0</v>
@@ -46436,7 +46421,7 @@
       <c r="Y86" s="100"/>
       <c r="Z86" s="100"/>
       <c r="AA86" s="94" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AB86" s="94">
         <v>-21.0</v>
@@ -46470,7 +46455,7 @@
       <c r="Y87" s="100"/>
       <c r="Z87" s="100"/>
       <c r="AA87" s="94" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AB87" s="94">
         <v>-7.0</v>
@@ -46504,7 +46489,7 @@
       <c r="Y88" s="100"/>
       <c r="Z88" s="100"/>
       <c r="AA88" s="94" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AB88" s="94">
         <v>-10.0</v>
@@ -46538,7 +46523,7 @@
       <c r="Y89" s="100"/>
       <c r="Z89" s="100"/>
       <c r="AA89" s="94" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AB89" s="94">
         <v>-6.0</v>
@@ -46631,7 +46616,7 @@
       <c r="Y92" s="100"/>
       <c r="Z92" s="100"/>
       <c r="AA92" s="94" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AB92" s="94">
         <v>-17.0</v>
@@ -46897,7 +46882,7 @@
       <c r="Y101" s="100"/>
       <c r="Z101" s="100"/>
       <c r="AA101" s="94" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AB101" s="94">
         <v>-6.0</v>
@@ -46931,7 +46916,7 @@
       <c r="Y102" s="100"/>
       <c r="Z102" s="100"/>
       <c r="AA102" s="94" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AB102" s="94">
         <v>1.0</v>
@@ -47023,7 +47008,7 @@
       <c r="Y105" s="100"/>
       <c r="Z105" s="100"/>
       <c r="AA105" s="94" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AB105" s="94">
         <v>-2.0</v>
@@ -47086,7 +47071,7 @@
       <c r="Y107" s="100"/>
       <c r="Z107" s="100"/>
       <c r="AA107" s="94" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AB107" s="94">
         <v>-12.0</v>
@@ -47178,7 +47163,7 @@
       <c r="Y110" s="100"/>
       <c r="Z110" s="100"/>
       <c r="AA110" s="94" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AB110" s="94">
         <v>-14.0</v>
@@ -47212,7 +47197,7 @@
       <c r="Y111" s="100"/>
       <c r="Z111" s="100"/>
       <c r="AA111" s="94" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AB111" s="94">
         <v>-6.0</v>
@@ -47246,7 +47231,7 @@
       <c r="Y112" s="100"/>
       <c r="Z112" s="100"/>
       <c r="AA112" s="94" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AB112" s="94">
         <v>-11.0</v>
@@ -47309,7 +47294,7 @@
       <c r="Y114" s="100"/>
       <c r="Z114" s="100"/>
       <c r="AA114" s="94" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AB114" s="94">
         <v>-1.0</v>
@@ -47401,7 +47386,7 @@
       <c r="Y117" s="100"/>
       <c r="Z117" s="100"/>
       <c r="AA117" s="94" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AB117" s="94">
         <v>12.0</v>
@@ -47464,7 +47449,7 @@
       <c r="Y119" s="100"/>
       <c r="Z119" s="100"/>
       <c r="AA119" s="94" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AB119" s="94">
         <v>-17.0</v>
@@ -47585,7 +47570,7 @@
       <c r="Y123" s="100"/>
       <c r="Z123" s="100"/>
       <c r="AA123" s="94" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AB123" s="94">
         <v>-15.0</v>
@@ -47736,7 +47721,7 @@
       <c r="Y128" s="100"/>
       <c r="Z128" s="100"/>
       <c r="AA128" s="94" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AB128" s="94">
         <v>-11.0</v>
@@ -48121,7 +48106,7 @@
       <c r="Y141" s="100"/>
       <c r="Z141" s="100"/>
       <c r="AA141" s="94" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AB141" s="94">
         <v>-10.0</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -1384,7 +1384,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46162.0</v>
+        <v>46164.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1413,7 +1413,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Středa</v>
+        <v>Pátek</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -2208,8 +2208,8 @@
       <c r="T5" s="84"/>
       <c r="U5" s="84"/>
       <c r="V5" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),111.5)</f>
-        <v>111.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),135.0)</f>
+        <v>135</v>
       </c>
       <c r="W5" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2274,8 +2274,8 @@
       <c r="T6" s="84"/>
       <c r="U6" s="84"/>
       <c r="V6" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.0)</f>
-        <v>114</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.5)</f>
+        <v>140.5</v>
       </c>
       <c r="W6" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2334,8 +2334,8 @@
       <c r="T7" s="84"/>
       <c r="U7" s="84"/>
       <c r="V7" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
-        <v>40</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.5)</f>
+        <v>64.5</v>
       </c>
       <c r="W7" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2403,8 +2403,8 @@
       <c r="T8" s="84"/>
       <c r="U8" s="84"/>
       <c r="V8" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
+        <v>119</v>
       </c>
       <c r="W8" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2466,8 +2466,8 @@
       <c r="T9" s="84"/>
       <c r="U9" s="84"/>
       <c r="V9" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),99.5)</f>
-        <v>99.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.5)</f>
+        <v>106.5</v>
       </c>
       <c r="W9" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2535,8 +2535,8 @@
       <c r="T10" s="84"/>
       <c r="U10" s="84"/>
       <c r="V10" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.5)</f>
-        <v>64.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),87.5)</f>
+        <v>87.5</v>
       </c>
       <c r="W10" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2595,12 +2595,12 @@
       <c r="T11" s="84"/>
       <c r="U11" s="84"/>
       <c r="V11" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
-        <v>70</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.5)</f>
+        <v>89.5</v>
       </c>
       <c r="W11" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13675.48)</f>
-        <v>13675.48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17088.153000000002)</f>
+        <v>17088.153</v>
       </c>
       <c r="X11" s="84"/>
       <c r="Y11" s="84"/>
@@ -2781,12 +2781,12 @@
       <c r="T14" s="84"/>
       <c r="U14" s="84"/>
       <c r="V14" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.0)</f>
+        <v>36</v>
       </c>
       <c r="W14" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3306.16)</f>
-        <v>3306.16</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5951.088)</f>
+        <v>5951.088</v>
       </c>
       <c r="X14" s="84"/>
       <c r="Y14" s="84"/>
@@ -2844,8 +2844,8 @@
       <c r="T15" s="84"/>
       <c r="U15" s="84"/>
       <c r="V15" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102.0)</f>
-        <v>102</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.5)</f>
+        <v>117.5</v>
       </c>
       <c r="W15" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2907,8 +2907,8 @@
       <c r="T16" s="84"/>
       <c r="U16" s="84"/>
       <c r="V16" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.0)</f>
-        <v>133</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
+        <v>148</v>
       </c>
       <c r="W16" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -3027,12 +3027,12 @@
       <c r="T18" s="84"/>
       <c r="U18" s="84"/>
       <c r="V18" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.5)</f>
+        <v>112.5</v>
       </c>
       <c r="W18" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16392.688000000002)</f>
-        <v>16392.688</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20241.05)</f>
+        <v>20241.05</v>
       </c>
       <c r="X18" s="84"/>
       <c r="Y18" s="84"/>
@@ -3087,12 +3087,12 @@
       <c r="T19" s="84"/>
       <c r="U19" s="84"/>
       <c r="V19" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.5)</f>
-        <v>66.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.5)</f>
+        <v>89.5</v>
       </c>
       <c r="W19" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14990.43)</f>
-        <v>14990.43</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19321.715)</f>
+        <v>19321.715</v>
       </c>
       <c r="X19" s="84"/>
       <c r="Y19" s="84"/>
@@ -3213,8 +3213,8 @@
       <c r="T21" s="84"/>
       <c r="U21" s="84"/>
       <c r="V21" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.0)</f>
+        <v>114</v>
       </c>
       <c r="W21" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3273,8 +3273,8 @@
       <c r="T22" s="84"/>
       <c r="U22" s="84"/>
       <c r="V22" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),174.5)</f>
-        <v>174.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),196.5)</f>
+        <v>196.5</v>
       </c>
       <c r="W22" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3396,12 +3396,12 @@
       <c r="T24" s="84"/>
       <c r="U24" s="84"/>
       <c r="V24" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),105.0)</f>
-        <v>105</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),129.5)</f>
+        <v>129.5</v>
       </c>
       <c r="W24" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17984.0)</f>
-        <v>17984</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21580.6)</f>
+        <v>21580.6</v>
       </c>
       <c r="X24" s="84"/>
       <c r="Y24" s="84"/>
@@ -3456,12 +3456,12 @@
       <c r="T25" s="84"/>
       <c r="U25" s="84"/>
       <c r="V25" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
-        <v>27</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
+        <v>33</v>
       </c>
       <c r="W25" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4129.164)</f>
-        <v>4129.164</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5046.756)</f>
+        <v>5046.756</v>
       </c>
       <c r="X25" s="84"/>
       <c r="Y25" s="84"/>
@@ -3621,7 +3621,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
         <v>Zličín</v>
       </c>
-      <c r="H28" s="84"/>
+      <c r="H28" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
+        <v>Prosek</v>
+      </c>
       <c r="I28" s="84"/>
       <c r="J28" s="84"/>
       <c r="K28" s="84"/>
@@ -3636,12 +3639,12 @@
       <c r="T28" s="84"/>
       <c r="U28" s="84"/>
       <c r="V28" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102.0)</f>
-        <v>102</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
+        <v>119</v>
       </c>
       <c r="W28" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17543.6)</f>
-        <v>17543.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20039.2)</f>
+        <v>20039.2</v>
       </c>
       <c r="X28" s="84"/>
       <c r="Y28" s="84"/>
@@ -3756,12 +3759,12 @@
       <c r="T30" s="84"/>
       <c r="U30" s="84"/>
       <c r="V30" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103.5)</f>
-        <v>103.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),124.5)</f>
+        <v>124.5</v>
       </c>
       <c r="W30" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16776.203)</f>
-        <v>16776.203</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19658.621000000003)</f>
+        <v>19658.621</v>
       </c>
       <c r="X30" s="84"/>
       <c r="Y30" s="84"/>
@@ -3822,12 +3825,12 @@
       <c r="T31" s="84"/>
       <c r="U31" s="84"/>
       <c r="V31" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.0)</f>
-        <v>78</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
+        <v>94</v>
       </c>
       <c r="W31" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11928.696)</f>
-        <v>11928.696</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14375.608)</f>
+        <v>14375.608</v>
       </c>
       <c r="X31" s="84"/>
       <c r="Y31" s="84"/>
@@ -4065,12 +4068,12 @@
       <c r="T35" s="84"/>
       <c r="U35" s="84"/>
       <c r="V35" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),72.0)</f>
-        <v>72</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
+        <v>88</v>
       </c>
       <c r="W35" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11902.176)</f>
-        <v>11902.176</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14547.104)</f>
+        <v>14547.104</v>
       </c>
       <c r="X35" s="84"/>
       <c r="Y35" s="84"/>
@@ -4185,12 +4188,12 @@
       <c r="T37" s="84"/>
       <c r="U37" s="84"/>
       <c r="V37" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.5)</f>
-        <v>21.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.0)</f>
+        <v>26</v>
       </c>
       <c r="W37" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3554.122)</f>
-        <v>3554.122</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4298.008)</f>
+        <v>4298.008</v>
       </c>
       <c r="X37" s="84"/>
       <c r="Y37" s="84"/>
@@ -4248,12 +4251,12 @@
       <c r="T38" s="84"/>
       <c r="U38" s="84"/>
       <c r="V38" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.5)</f>
-        <v>90.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),99.5)</f>
+        <v>99.5</v>
       </c>
       <c r="W38" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14960.374)</f>
-        <v>14960.374</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16227.171)</f>
+        <v>16227.171</v>
       </c>
       <c r="X38" s="84"/>
       <c r="Y38" s="84"/>
@@ -4317,12 +4320,12 @@
       <c r="T39" s="84"/>
       <c r="U39" s="84"/>
       <c r="V39" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.5)</f>
-        <v>106.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.5)</f>
+        <v>119.5</v>
       </c>
       <c r="W39" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17187.977)</f>
-        <v>17187.977</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18972.331)</f>
+        <v>18972.331</v>
       </c>
       <c r="X39" s="84"/>
       <c r="Y39" s="84"/>
@@ -4437,12 +4440,12 @@
       <c r="T41" s="84"/>
       <c r="U41" s="84"/>
       <c r="V41" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),99.0)</f>
-        <v>99</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
+        <v>112</v>
       </c>
       <c r="W41" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16158.542)</f>
-        <v>16158.542</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17942.896)</f>
+        <v>17942.896</v>
       </c>
       <c r="X41" s="84"/>
       <c r="Y41" s="84"/>
@@ -5358,12 +5361,12 @@
       <c r="T60" s="84"/>
       <c r="U60" s="84"/>
       <c r="V60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2364.0)</f>
-        <v>2364</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2769.0)</f>
+        <v>2769</v>
       </c>
       <c r="W60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),793844.2679999996)</f>
-        <v>793844.268</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),828644.9569999998)</f>
+        <v>828644.957</v>
       </c>
       <c r="X60" s="84"/>
       <c r="Y60" s="84"/>
@@ -6045,12 +6048,12 @@
       <c r="T75" s="84"/>
       <c r="U75" s="84"/>
       <c r="V75" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.0)</f>
-        <v>59</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),71.5)</f>
+        <v>71.5</v>
       </c>
       <c r="W75" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8850.0)</f>
-        <v>8850</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10725.0)</f>
+        <v>10725</v>
       </c>
       <c r="X75" s="84"/>
       <c r="Y75" s="84"/>
@@ -6102,12 +6105,12 @@
       <c r="T76" s="84"/>
       <c r="U76" s="84"/>
       <c r="V76" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.0)</f>
-        <v>63</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),87.0)</f>
+        <v>87</v>
       </c>
       <c r="W76" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11138.4)</f>
-        <v>11138.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15341.6)</f>
+        <v>15341.6</v>
       </c>
       <c r="X76" s="84"/>
       <c r="Y76" s="84"/>
@@ -6216,12 +6219,12 @@
       <c r="T78" s="84"/>
       <c r="U78" s="84"/>
       <c r="V78" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
-        <v>25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
+        <v>30</v>
       </c>
       <c r="W78" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4420.0)</f>
-        <v>4420</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5304.0)</f>
+        <v>5304</v>
       </c>
       <c r="X78" s="84"/>
       <c r="Y78" s="84"/>
@@ -6279,12 +6282,12 @@
       <c r="T79" s="84"/>
       <c r="U79" s="84"/>
       <c r="V79" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
-        <v>18</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
+        <v>23</v>
       </c>
       <c r="W79" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2752.776)</f>
-        <v>2752.776</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3517.436)</f>
+        <v>3517.436</v>
       </c>
       <c r="X79" s="84"/>
       <c r="Y79" s="84"/>
@@ -6402,12 +6405,12 @@
       <c r="T81" s="84"/>
       <c r="U81" s="84"/>
       <c r="V81" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),96.5)</f>
-        <v>96.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.5)</f>
+        <v>106.5</v>
       </c>
       <c r="W81" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14757.938)</f>
-        <v>14757.938</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16093.583)</f>
+        <v>16093.583</v>
       </c>
       <c r="X81" s="84"/>
       <c r="Y81" s="84"/>
@@ -6576,12 +6579,12 @@
       <c r="T84" s="84"/>
       <c r="U84" s="84"/>
       <c r="V84" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.0)</f>
-        <v>33</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
+        <v>39</v>
       </c>
       <c r="W84" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5455.164)</f>
-        <v>5455.164</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6447.012)</f>
+        <v>6447.012</v>
       </c>
       <c r="X84" s="84"/>
       <c r="Y84" s="84"/>
@@ -6633,12 +6636,12 @@
       <c r="T85" s="84"/>
       <c r="U85" s="84"/>
       <c r="V85" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
-        <v>27</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
+        <v>30</v>
       </c>
       <c r="W85" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4050.0)</f>
-        <v>4050</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4500.0)</f>
+        <v>4500</v>
       </c>
       <c r="X85" s="84"/>
       <c r="Y85" s="84"/>
@@ -6747,12 +6750,12 @@
       <c r="T87" s="84"/>
       <c r="U87" s="84"/>
       <c r="V87" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
+        <v>13</v>
       </c>
       <c r="W87" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1529.32)</f>
-        <v>1529.32</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1988.116)</f>
+        <v>1988.116</v>
       </c>
       <c r="X87" s="84"/>
       <c r="Y87" s="84"/>
@@ -6873,12 +6876,12 @@
       <c r="T89" s="84"/>
       <c r="U89" s="84"/>
       <c r="V89" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
-        <v>42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
+        <v>55</v>
       </c>
       <c r="W89" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7140.0)</f>
-        <v>7140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9350.0)</f>
+        <v>9350</v>
       </c>
       <c r="X89" s="84"/>
       <c r="Y89" s="84"/>
@@ -6933,12 +6936,12 @@
       <c r="T90" s="84"/>
       <c r="U90" s="84"/>
       <c r="V90" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
-        <v>74</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
+        <v>81</v>
       </c>
       <c r="W90" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11840.0)</f>
-        <v>11840</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12960.0)</f>
+        <v>12960</v>
       </c>
       <c r="X90" s="84"/>
       <c r="Y90" s="84"/>
@@ -7098,12 +7101,12 @@
       <c r="T93" s="84"/>
       <c r="U93" s="84"/>
       <c r="V93" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.5)</f>
-        <v>133.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
       </c>
       <c r="W93" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20893.943)</f>
-        <v>20893.943</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21786.12)</f>
+        <v>21786.12</v>
       </c>
       <c r="X93" s="84"/>
       <c r="Y93" s="84"/>
@@ -7161,12 +7164,12 @@
       <c r="T94" s="84"/>
       <c r="U94" s="84"/>
       <c r="V94" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),120.0)</f>
-        <v>120</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
+        <v>148</v>
       </c>
       <c r="W94" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19040.96)</f>
-        <v>19040.96</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22884.183999999997)</f>
+        <v>22884.184</v>
       </c>
       <c r="X94" s="84"/>
       <c r="Y94" s="84"/>
@@ -7278,8 +7281,8 @@
       <c r="T96" s="84"/>
       <c r="U96" s="84"/>
       <c r="V96" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.0)</f>
-        <v>65</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),77.0)</f>
+        <v>77</v>
       </c>
       <c r="W96" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44995.2)</f>
@@ -7335,12 +7338,12 @@
       <c r="T97" s="84"/>
       <c r="U97" s="84"/>
       <c r="V97" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
-        <v>38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.0)</f>
+        <v>45</v>
       </c>
       <c r="W97" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6281.704)</f>
-        <v>6281.704</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7438.86)</f>
+        <v>7438.86</v>
       </c>
       <c r="X97" s="84"/>
       <c r="Y97" s="84"/>
@@ -7401,12 +7404,12 @@
       <c r="T98" s="84"/>
       <c r="U98" s="84"/>
       <c r="V98" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.5)</f>
+        <v>24.5</v>
       </c>
       <c r="W98" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1697.28)</f>
-        <v>1697.28</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3465.2799999999997)</f>
+        <v>3465.28</v>
       </c>
       <c r="X98" s="84"/>
       <c r="Y98" s="84"/>
@@ -7791,12 +7794,12 @@
       <c r="T105" s="84"/>
       <c r="U105" s="84"/>
       <c r="V105" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.5)</f>
-        <v>55.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.0)</f>
+        <v>64</v>
       </c>
       <c r="W105" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8487.726)</f>
-        <v>8487.726</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9787.648)</f>
+        <v>9787.648</v>
       </c>
       <c r="X105" s="84"/>
       <c r="Y105" s="84"/>
@@ -7899,12 +7902,12 @@
       <c r="T107" s="84"/>
       <c r="U107" s="84"/>
       <c r="V107" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.5)</f>
-        <v>113.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),136.5)</f>
+        <v>136.5</v>
       </c>
       <c r="W107" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15890.0)</f>
-        <v>15890</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19110.0)</f>
+        <v>19110</v>
       </c>
       <c r="X107" s="84"/>
       <c r="Y107" s="84"/>
@@ -8475,12 +8478,12 @@
       <c r="T117" s="84"/>
       <c r="U117" s="84"/>
       <c r="V117" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),123.0)</f>
-        <v>123</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),135.0)</f>
+        <v>135</v>
       </c>
       <c r="W117" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19452.733999999997)</f>
-        <v>19452.734</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21099.83)</f>
+        <v>21099.83</v>
       </c>
       <c r="X117" s="84"/>
       <c r="Y117" s="84"/>
@@ -8640,12 +8643,12 @@
       <c r="T120" s="84"/>
       <c r="U120" s="84"/>
       <c r="V120" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
-        <v>18</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
+        <v>27</v>
       </c>
       <c r="W120" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2545.92)</f>
-        <v>2545.92</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3818.88)</f>
+        <v>3818.88</v>
       </c>
       <c r="X120" s="84"/>
       <c r="Y120" s="84"/>
@@ -8910,12 +8913,12 @@
       <c r="T125" s="84"/>
       <c r="U125" s="84"/>
       <c r="V125" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
-        <v>35</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.0)</f>
+        <v>47</v>
       </c>
       <c r="W125" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5352.62)</f>
-        <v>5352.62</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7187.804)</f>
+        <v>7187.804</v>
       </c>
       <c r="X125" s="84"/>
       <c r="Y125" s="84"/>
@@ -8967,12 +8970,12 @@
       <c r="T126" s="84"/>
       <c r="U126" s="84"/>
       <c r="V126" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.5)</f>
-        <v>29.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
+        <v>37</v>
       </c>
       <c r="W126" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4511.494)</f>
-        <v>4511.494</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5658.484)</f>
+        <v>5658.484</v>
       </c>
       <c r="X126" s="84"/>
       <c r="Y126" s="84"/>
@@ -12456,12 +12459,12 @@
       <c r="T196" s="84"/>
       <c r="U196" s="84"/>
       <c r="V196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1575.0)</f>
-        <v>1575</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1801.5)</f>
+        <v>1801.5</v>
       </c>
       <c r="W196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),309747.45900000003)</f>
-        <v>309747.459</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),342123.317)</f>
+        <v>342123.317</v>
       </c>
       <c r="X196" s="84"/>
       <c r="Y196" s="84"/>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="69">
   <si>
     <t>Výroba</t>
   </si>
@@ -69,7 +69,13 @@
     <t>Počet dní</t>
   </si>
   <si>
-    <t>Lažek Jaroslav</t>
+    <t>Paziak Viktoriia</t>
+  </si>
+  <si>
+    <t>Stepanenko Solomiia</t>
+  </si>
+  <si>
+    <t>Kursheva Diana</t>
   </si>
   <si>
     <t>Manažeři</t>
@@ -106,9 +112,6 @@
   </si>
   <si>
     <t>01:00</t>
-  </si>
-  <si>
-    <t>Stepanenko Solomiia</t>
   </si>
   <si>
     <t>10:00</t>
@@ -1384,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46164.0</v>
+        <v>46173.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1413,7 +1416,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Pátek</v>
+        <v>Neděle</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1734,13 +1737,13 @@
         <v>Výroba</v>
       </c>
       <c r="C1" s="62">
-        <v>46151.0</v>
+        <v>46101.0</v>
       </c>
       <c r="D1" s="63" t="s">
         <v>14</v>
       </c>
       <c r="E1" s="62">
-        <v>46151.0</v>
+        <v>46101.0</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>2</v>
@@ -1756,7 +1759,7 @@
       <c r="D2" s="12"/>
       <c r="E2" s="13"/>
       <c r="F2" s="65">
-        <v>0.0</v>
+        <v>41620.0</v>
       </c>
       <c r="H2" s="16"/>
     </row>
@@ -1764,12 +1767,12 @@
       <c r="A3" s="66"/>
       <c r="B3" s="67" t="str">
         <f>CHOOSE(WEEKDAY(C1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Sobota</v>
+        <v>Pátek</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="67" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Sobota</v>
+        <v>Pátek</v>
       </c>
       <c r="E3" s="5"/>
       <c r="H3" s="16"/>
@@ -1876,20 +1879,32 @@
         <v>1.0</v>
       </c>
       <c r="D10" s="82">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="71"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="82"/>
+      <c r="B11" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="D11" s="82">
+        <v>8.0</v>
+      </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="71"/>
-      <c r="B12" s="80"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="82"/>
+      <c r="B12" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="D12" s="82">
+        <v>8.0</v>
+      </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="71"/>
@@ -2108,10 +2123,10 @@
     </row>
     <row r="4">
       <c r="A4" s="88" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -2208,8 +2223,8 @@
       <c r="T5" s="84"/>
       <c r="U5" s="84"/>
       <c r="V5" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),135.0)</f>
-        <v>135</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),223.0)</f>
+        <v>223</v>
       </c>
       <c r="W5" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2274,8 +2289,8 @@
       <c r="T6" s="84"/>
       <c r="U6" s="84"/>
       <c r="V6" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.5)</f>
-        <v>140.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.5)</f>
+        <v>177.5</v>
       </c>
       <c r="W6" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2334,8 +2349,8 @@
       <c r="T7" s="84"/>
       <c r="U7" s="84"/>
       <c r="V7" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.5)</f>
-        <v>64.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.5)</f>
+        <v>110.5</v>
       </c>
       <c r="W7" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2403,8 +2418,8 @@
       <c r="T8" s="84"/>
       <c r="U8" s="84"/>
       <c r="V8" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
-        <v>119</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),190.0)</f>
+        <v>190</v>
       </c>
       <c r="W8" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2466,8 +2481,8 @@
       <c r="T9" s="84"/>
       <c r="U9" s="84"/>
       <c r="V9" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.5)</f>
-        <v>106.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),173.5)</f>
+        <v>173.5</v>
       </c>
       <c r="W9" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2535,8 +2550,8 @@
       <c r="T10" s="84"/>
       <c r="U10" s="84"/>
       <c r="V10" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),87.5)</f>
-        <v>87.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),160.0)</f>
+        <v>160</v>
       </c>
       <c r="W10" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2595,12 +2610,12 @@
       <c r="T11" s="84"/>
       <c r="U11" s="84"/>
       <c r="V11" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.5)</f>
-        <v>89.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.5)</f>
+        <v>110.5</v>
       </c>
       <c r="W11" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17088.153000000002)</f>
-        <v>17088.153</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20494.647)</f>
+        <v>20494.647</v>
       </c>
       <c r="X11" s="84"/>
       <c r="Y11" s="84"/>
@@ -2715,8 +2730,8 @@
       <c r="T13" s="84"/>
       <c r="U13" s="84"/>
       <c r="V13" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
-        <v>66</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
       </c>
       <c r="W13" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2781,12 +2796,12 @@
       <c r="T14" s="84"/>
       <c r="U14" s="84"/>
       <c r="V14" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.0)</f>
-        <v>36</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.5)</f>
+        <v>54.5</v>
       </c>
       <c r="W14" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5951.088)</f>
-        <v>5951.088</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9009.286)</f>
+        <v>9009.286</v>
       </c>
       <c r="X14" s="84"/>
       <c r="Y14" s="84"/>
@@ -2844,8 +2859,8 @@
       <c r="T15" s="84"/>
       <c r="U15" s="84"/>
       <c r="V15" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.5)</f>
-        <v>117.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),169.5)</f>
+        <v>169.5</v>
       </c>
       <c r="W15" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2907,8 +2922,8 @@
       <c r="T16" s="84"/>
       <c r="U16" s="84"/>
       <c r="V16" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
-        <v>148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
+        <v>153</v>
       </c>
       <c r="W16" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2967,12 +2982,12 @@
       <c r="T17" s="84"/>
       <c r="U17" s="84"/>
       <c r="V17" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.5)</f>
-        <v>22.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.5)</f>
+        <v>43.5</v>
       </c>
       <c r="W17" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3978.0)</f>
-        <v>3978</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7690.8)</f>
+        <v>7690.8</v>
       </c>
       <c r="X17" s="84"/>
       <c r="Y17" s="84"/>
@@ -3027,12 +3042,12 @@
       <c r="T18" s="84"/>
       <c r="U18" s="84"/>
       <c r="V18" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.5)</f>
-        <v>112.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.5)</f>
+        <v>126.5</v>
       </c>
       <c r="W18" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20241.05)</f>
-        <v>20241.05</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22440.113999999998)</f>
+        <v>22440.114</v>
       </c>
       <c r="X18" s="84"/>
       <c r="Y18" s="84"/>
@@ -3087,12 +3102,12 @@
       <c r="T19" s="84"/>
       <c r="U19" s="84"/>
       <c r="V19" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),89.5)</f>
-        <v>89.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.5)</f>
+        <v>153.5</v>
       </c>
       <c r="W19" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19321.715)</f>
-        <v>19321.715</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31300.595)</f>
+        <v>31300.595</v>
       </c>
       <c r="X19" s="84"/>
       <c r="Y19" s="84"/>
@@ -3198,7 +3213,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
         <v>Malešice</v>
       </c>
-      <c r="H21" s="84"/>
+      <c r="H21" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
       <c r="I21" s="84"/>
       <c r="J21" s="84"/>
       <c r="K21" s="84"/>
@@ -3213,8 +3231,8 @@
       <c r="T21" s="84"/>
       <c r="U21" s="84"/>
       <c r="V21" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),114.0)</f>
-        <v>114</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),156.0)</f>
+        <v>156</v>
       </c>
       <c r="W21" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3273,8 +3291,8 @@
       <c r="T22" s="84"/>
       <c r="U22" s="84"/>
       <c r="V22" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),196.5)</f>
-        <v>196.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),255.5)</f>
+        <v>255.5</v>
       </c>
       <c r="W22" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3396,12 +3414,12 @@
       <c r="T24" s="84"/>
       <c r="U24" s="84"/>
       <c r="V24" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),129.5)</f>
-        <v>129.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
+        <v>176</v>
       </c>
       <c r="W24" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21580.6)</f>
-        <v>21580.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28406.8)</f>
+        <v>28406.8</v>
       </c>
       <c r="X24" s="84"/>
       <c r="Y24" s="84"/>
@@ -3570,12 +3588,12 @@
       <c r="T27" s="84"/>
       <c r="U27" s="84"/>
       <c r="V27" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.5)</f>
-        <v>47.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.5)</f>
+        <v>59.5</v>
       </c>
       <c r="W27" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8985.86)</f>
-        <v>8985.86</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11255.972)</f>
+        <v>11255.972</v>
       </c>
       <c r="X27" s="84"/>
       <c r="Y27" s="84"/>
@@ -3610,12 +3628,12 @@
         <v>Yarushynskyi Vladyslav</v>
       </c>
       <c r="E28" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
+      <c r="F28" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
         <v>Chodov</v>
-      </c>
-      <c r="F28" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
-        <v>Malešice</v>
       </c>
       <c r="G28" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
@@ -3639,12 +3657,12 @@
       <c r="T28" s="84"/>
       <c r="U28" s="84"/>
       <c r="V28" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
-        <v>119</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),166.5)</f>
+        <v>166.5</v>
       </c>
       <c r="W28" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20039.2)</f>
-        <v>20039.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27012.2)</f>
+        <v>27012.2</v>
       </c>
       <c r="X28" s="84"/>
       <c r="Y28" s="84"/>
@@ -3759,12 +3777,12 @@
       <c r="T30" s="84"/>
       <c r="U30" s="84"/>
       <c r="V30" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),124.5)</f>
-        <v>124.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),169.5)</f>
+        <v>169.5</v>
       </c>
       <c r="W30" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19658.621000000003)</f>
-        <v>19658.621</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25835.231)</f>
+        <v>25835.231</v>
       </c>
       <c r="X30" s="84"/>
       <c r="Y30" s="84"/>
@@ -3825,12 +3843,12 @@
       <c r="T31" s="84"/>
       <c r="U31" s="84"/>
       <c r="V31" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),94.0)</f>
-        <v>94</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.5)</f>
+        <v>117.5</v>
       </c>
       <c r="W31" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14375.608)</f>
-        <v>14375.608</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17490.385000000002)</f>
+        <v>17490.385</v>
       </c>
       <c r="X31" s="84"/>
       <c r="Y31" s="84"/>
@@ -4068,12 +4086,12 @@
       <c r="T35" s="84"/>
       <c r="U35" s="84"/>
       <c r="V35" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),88.0)</f>
-        <v>88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),134.0)</f>
+        <v>134</v>
       </c>
       <c r="W35" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14547.104)</f>
-        <v>14547.104</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20962.572)</f>
+        <v>20962.572</v>
       </c>
       <c r="X35" s="84"/>
       <c r="Y35" s="84"/>
@@ -4188,12 +4206,12 @@
       <c r="T37" s="84"/>
       <c r="U37" s="84"/>
       <c r="V37" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.0)</f>
-        <v>26</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.5)</f>
+        <v>37.5</v>
       </c>
       <c r="W37" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4298.008)</f>
-        <v>4298.008</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6199.05)</f>
+        <v>6199.05</v>
       </c>
       <c r="X37" s="84"/>
       <c r="Y37" s="84"/>
@@ -4251,12 +4269,12 @@
       <c r="T38" s="84"/>
       <c r="U38" s="84"/>
       <c r="V38" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),99.5)</f>
-        <v>99.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),154.5)</f>
+        <v>154.5</v>
       </c>
       <c r="W38" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16227.171)</f>
-        <v>16227.171</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23776.361)</f>
+        <v>23776.361</v>
       </c>
       <c r="X38" s="84"/>
       <c r="Y38" s="84"/>
@@ -4320,12 +4338,12 @@
       <c r="T39" s="84"/>
       <c r="U39" s="84"/>
       <c r="V39" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.5)</f>
-        <v>119.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),164.0)</f>
+        <v>164</v>
       </c>
       <c r="W39" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18972.331)</f>
-        <v>18972.331</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25080.311999999998)</f>
+        <v>25080.312</v>
       </c>
       <c r="X39" s="84"/>
       <c r="Y39" s="84"/>
@@ -4380,12 +4398,12 @@
       <c r="T40" s="84"/>
       <c r="U40" s="84"/>
       <c r="V40" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
+        <v>23</v>
       </c>
       <c r="W40" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3802.084)</f>
+        <v>3802.084</v>
       </c>
       <c r="X40" s="84"/>
       <c r="Y40" s="84"/>
@@ -4440,12 +4458,12 @@
       <c r="T41" s="84"/>
       <c r="U41" s="84"/>
       <c r="V41" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),112.0)</f>
-        <v>112</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.5)</f>
+        <v>150.5</v>
       </c>
       <c r="W41" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17942.896)</f>
-        <v>17942.896</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23227.328999999998)</f>
+        <v>23227.329</v>
       </c>
       <c r="X41" s="84"/>
       <c r="Y41" s="84"/>
@@ -5361,12 +5379,12 @@
       <c r="T60" s="84"/>
       <c r="U60" s="84"/>
       <c r="V60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2769.0)</f>
-        <v>2769</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3884.0)</f>
+        <v>3884</v>
       </c>
       <c r="W60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),828644.9569999998)</f>
-        <v>828644.957</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),909421.29)</f>
+        <v>909421.29</v>
       </c>
       <c r="X60" s="84"/>
       <c r="Y60" s="84"/>
@@ -6048,12 +6066,12 @@
       <c r="T75" s="84"/>
       <c r="U75" s="84"/>
       <c r="V75" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),71.5)</f>
-        <v>71.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.5)</f>
+        <v>92.5</v>
       </c>
       <c r="W75" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10725.0)</f>
-        <v>10725</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13875.0)</f>
+        <v>13875</v>
       </c>
       <c r="X75" s="84"/>
       <c r="Y75" s="84"/>
@@ -6105,12 +6123,12 @@
       <c r="T76" s="84"/>
       <c r="U76" s="84"/>
       <c r="V76" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),87.0)</f>
-        <v>87</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),131.0)</f>
+        <v>131</v>
       </c>
       <c r="W76" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15341.6)</f>
-        <v>15341.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21800.8)</f>
+        <v>21800.8</v>
       </c>
       <c r="X76" s="84"/>
       <c r="Y76" s="84"/>
@@ -6345,12 +6363,12 @@
       <c r="T80" s="84"/>
       <c r="U80" s="84"/>
       <c r="V80" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.5)</f>
-        <v>55.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),82.5)</f>
+        <v>82.5</v>
       </c>
       <c r="W80" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9174.594000000001)</f>
-        <v>9174.594</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13637.91)</f>
+        <v>13637.91</v>
       </c>
       <c r="X80" s="84"/>
       <c r="Y80" s="84"/>
@@ -6405,12 +6423,12 @@
       <c r="T81" s="84"/>
       <c r="U81" s="84"/>
       <c r="V81" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.5)</f>
-        <v>106.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),149.5)</f>
+        <v>149.5</v>
       </c>
       <c r="W81" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16093.583)</f>
-        <v>16093.583</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21553.808999999997)</f>
+        <v>21553.809</v>
       </c>
       <c r="X81" s="84"/>
       <c r="Y81" s="84"/>
@@ -6519,12 +6537,12 @@
       <c r="T83" s="84"/>
       <c r="U83" s="84"/>
       <c r="V83" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
-        <v>24</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.5)</f>
+        <v>30.5</v>
       </c>
       <c r="W83" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3670.368)</f>
-        <v>3670.368</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4664.426)</f>
+        <v>4664.426</v>
       </c>
       <c r="X83" s="84"/>
       <c r="Y83" s="84"/>
@@ -6579,12 +6597,12 @@
       <c r="T84" s="84"/>
       <c r="U84" s="84"/>
       <c r="V84" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
-        <v>39</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.5)</f>
+        <v>51.5</v>
       </c>
       <c r="W84" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6447.012)</f>
-        <v>6447.012</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8513.362000000001)</f>
+        <v>8513.362</v>
       </c>
       <c r="X84" s="84"/>
       <c r="Y84" s="84"/>
@@ -6636,12 +6654,12 @@
       <c r="T85" s="84"/>
       <c r="U85" s="84"/>
       <c r="V85" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
+        <v>40</v>
       </c>
       <c r="W85" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4500.0)</f>
-        <v>4500</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6000.0)</f>
+        <v>6000</v>
       </c>
       <c r="X85" s="84"/>
       <c r="Y85" s="84"/>
@@ -6750,12 +6768,12 @@
       <c r="T87" s="84"/>
       <c r="U87" s="84"/>
       <c r="V87" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
-        <v>13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
+        <v>18</v>
       </c>
       <c r="W87" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1988.116)</f>
-        <v>1988.116</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2752.776)</f>
+        <v>2752.776</v>
       </c>
       <c r="X87" s="84"/>
       <c r="Y87" s="84"/>
@@ -6876,12 +6894,12 @@
       <c r="T89" s="84"/>
       <c r="U89" s="84"/>
       <c r="V89" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
-        <v>55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
+        <v>76</v>
       </c>
       <c r="W89" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9350.0)</f>
-        <v>9350</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12920.0)</f>
+        <v>12920</v>
       </c>
       <c r="X89" s="84"/>
       <c r="Y89" s="84"/>
@@ -6936,12 +6954,12 @@
       <c r="T90" s="84"/>
       <c r="U90" s="84"/>
       <c r="V90" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.0)</f>
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
+        <v>117</v>
       </c>
       <c r="W90" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12960.0)</f>
-        <v>12960</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18720.0)</f>
+        <v>18720</v>
       </c>
       <c r="X90" s="84"/>
       <c r="Y90" s="84"/>
@@ -7101,12 +7119,12 @@
       <c r="T93" s="84"/>
       <c r="U93" s="84"/>
       <c r="V93" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),194.5)</f>
+        <v>194.5</v>
       </c>
       <c r="W93" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21786.12)</f>
-        <v>21786.12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29266.680999999997)</f>
+        <v>29266.681</v>
       </c>
       <c r="X93" s="84"/>
       <c r="Y93" s="84"/>
@@ -7164,12 +7182,12 @@
       <c r="T94" s="84"/>
       <c r="U94" s="84"/>
       <c r="V94" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
-        <v>148</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
+        <v>242</v>
       </c>
       <c r="W94" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22884.183999999997)</f>
-        <v>22884.184</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35786.436)</f>
+        <v>35786.436</v>
       </c>
       <c r="X94" s="84"/>
       <c r="Y94" s="84"/>
@@ -7281,8 +7299,8 @@
       <c r="T96" s="84"/>
       <c r="U96" s="84"/>
       <c r="V96" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),77.0)</f>
-        <v>77</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),130.0)</f>
+        <v>130</v>
       </c>
       <c r="W96" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44995.2)</f>
@@ -7338,12 +7356,12 @@
       <c r="T97" s="84"/>
       <c r="U97" s="84"/>
       <c r="V97" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.0)</f>
-        <v>45</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
+        <v>70</v>
       </c>
       <c r="W97" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7438.86)</f>
-        <v>7438.86</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11571.56)</f>
+        <v>11571.56</v>
       </c>
       <c r="X97" s="84"/>
       <c r="Y97" s="84"/>
@@ -7461,12 +7479,12 @@
       <c r="T99" s="84"/>
       <c r="U99" s="84"/>
       <c r="V99" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
-        <v>34</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.0)</f>
+        <v>53</v>
       </c>
       <c r="W99" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4808.96)</f>
-        <v>4808.96</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7496.32)</f>
+        <v>7496.32</v>
       </c>
       <c r="X99" s="84"/>
       <c r="Y99" s="84"/>
@@ -7794,12 +7812,12 @@
       <c r="T105" s="84"/>
       <c r="U105" s="84"/>
       <c r="V105" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.0)</f>
-        <v>64</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
+        <v>98</v>
       </c>
       <c r="W105" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9787.648)</f>
-        <v>9787.648</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14987.336)</f>
+        <v>14987.336</v>
       </c>
       <c r="X105" s="84"/>
       <c r="Y105" s="84"/>
@@ -7902,12 +7920,12 @@
       <c r="T107" s="84"/>
       <c r="U107" s="84"/>
       <c r="V107" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),136.5)</f>
-        <v>136.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.0)</f>
+        <v>198</v>
       </c>
       <c r="W107" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19110.0)</f>
-        <v>19110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27720.0)</f>
+        <v>27720</v>
       </c>
       <c r="X107" s="84"/>
       <c r="Y107" s="84"/>
@@ -7962,12 +7980,12 @@
       <c r="T108" s="84"/>
       <c r="U108" s="84"/>
       <c r="V108" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.5)</f>
-        <v>64.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.5)</f>
+        <v>76.5</v>
       </c>
       <c r="W108" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10662.366)</f>
-        <v>10662.366</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12646.062)</f>
+        <v>12646.062</v>
       </c>
       <c r="X108" s="84"/>
       <c r="Y108" s="84"/>
@@ -8364,12 +8382,12 @@
       <c r="T115" s="84"/>
       <c r="U115" s="84"/>
       <c r="V115" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.5)</f>
-        <v>31.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.5)</f>
+        <v>44.5</v>
       </c>
       <c r="W115" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5207.202)</f>
-        <v>5207.202</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7356.206)</f>
+        <v>7356.206</v>
       </c>
       <c r="X115" s="84"/>
       <c r="Y115" s="84"/>
@@ -8478,12 +8496,12 @@
       <c r="T117" s="84"/>
       <c r="U117" s="84"/>
       <c r="V117" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),135.0)</f>
-        <v>135</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.0)</f>
+        <v>182</v>
       </c>
       <c r="W117" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21099.83)</f>
-        <v>21099.83</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27550.956)</f>
+        <v>27550.956</v>
       </c>
       <c r="X117" s="84"/>
       <c r="Y117" s="84"/>
@@ -8586,12 +8604,12 @@
       <c r="T119" s="84"/>
       <c r="U119" s="84"/>
       <c r="V119" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
-        <v>25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.0)</f>
+        <v>32</v>
       </c>
       <c r="W119" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3536.0)</f>
-        <v>3536</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4526.08)</f>
+        <v>4526.08</v>
       </c>
       <c r="X119" s="84"/>
       <c r="Y119" s="84"/>
@@ -8643,12 +8661,12 @@
       <c r="T120" s="84"/>
       <c r="U120" s="84"/>
       <c r="V120" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
-        <v>27</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.5)</f>
+        <v>30.5</v>
       </c>
       <c r="W120" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3818.88)</f>
-        <v>3818.88</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4313.92)</f>
+        <v>4313.92</v>
       </c>
       <c r="X120" s="84"/>
       <c r="Y120" s="84"/>
@@ -8913,12 +8931,12 @@
       <c r="T125" s="84"/>
       <c r="U125" s="84"/>
       <c r="V125" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.0)</f>
-        <v>47</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),53.0)</f>
+        <v>53</v>
       </c>
       <c r="W125" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7187.804)</f>
-        <v>7187.804</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8105.396)</f>
+        <v>8105.396</v>
       </c>
       <c r="X125" s="84"/>
       <c r="Y125" s="84"/>
@@ -8946,8 +8964,8 @@
         <v>0</v>
       </c>
       <c r="D126" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pavel Břicháč")</f>
-        <v>Pavel Břicháč</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Břicháč Pavel")</f>
+        <v>Břicháč Pavel</v>
       </c>
       <c r="E126" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
@@ -8970,12 +8988,12 @@
       <c r="T126" s="84"/>
       <c r="U126" s="84"/>
       <c r="V126" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.0)</f>
-        <v>37</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.5)</f>
+        <v>65.5</v>
       </c>
       <c r="W126" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5658.484)</f>
-        <v>5658.484</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10017.046)</f>
+        <v>10017.046</v>
       </c>
       <c r="X126" s="84"/>
       <c r="Y126" s="84"/>
@@ -9002,8 +9020,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D127" s="84"/>
-      <c r="E127" s="84"/>
+      <c r="D127" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Čerešňák Michal")</f>
+        <v>Čerešňák Michal</v>
+      </c>
+      <c r="E127" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
+        <v>Zličín</v>
+      </c>
       <c r="F127" s="84"/>
       <c r="G127" s="84"/>
       <c r="H127" s="84"/>
@@ -9020,10 +9044,13 @@
       <c r="S127" s="84"/>
       <c r="T127" s="84"/>
       <c r="U127" s="84"/>
-      <c r="V127" s="84"/>
+      <c r="V127" s="90">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
+      </c>
       <c r="W127" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3230.0)</f>
+        <v>3230</v>
       </c>
       <c r="X127" s="84"/>
       <c r="Y127" s="84"/>
@@ -12459,12 +12486,12 @@
       <c r="T196" s="84"/>
       <c r="U196" s="84"/>
       <c r="V196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1801.5)</f>
-        <v>1801.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2504.5)</f>
+        <v>2504.5</v>
       </c>
       <c r="W196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),342123.317)</f>
-        <v>342123.317</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),437898.78799999994)</f>
+        <v>437898.788</v>
       </c>
       <c r="X196" s="84"/>
       <c r="Y196" s="84"/>
@@ -43854,7 +43881,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C1" s="94" t="s">
         <v>4</v>
@@ -43866,16 +43893,16 @@
         <v>8</v>
       </c>
       <c r="F1" s="94" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G1" s="94" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="94" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1" s="94" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J1" s="94" t="s">
         <v>12</v>
@@ -43889,22 +43916,22 @@
         <v>45528.0</v>
       </c>
       <c r="B2" s="94" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" s="94" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" s="96" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" s="96" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F2" s="96" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2" s="96" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H2" s="97">
         <v>3728.0</v>
@@ -43915,22 +43942,22 @@
         <v>45528.0</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" s="94" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="96" t="s">
+      <c r="G3" s="96" t="s">
         <v>31</v>
-      </c>
-      <c r="E3" s="96" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="96" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="96" t="s">
-        <v>29</v>
       </c>
       <c r="H3" s="97">
         <v>3728.0</v>
@@ -43941,19 +43968,19 @@
         <v>45528.0</v>
       </c>
       <c r="B4" s="94" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H4" s="97">
         <v>3728.0</v>
@@ -43964,7 +43991,7 @@
         <v>45528.0</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I5" s="97">
         <v>12.0</v>
@@ -43981,22 +44008,22 @@
         <v>45526.0</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="94" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" s="96" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="96" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F6" s="96" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G6" s="96" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H6" s="97">
         <v>3728.0</v>
@@ -44007,22 +44034,22 @@
         <v>45526.0</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="94" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="96" t="s">
+      <c r="G7" s="96" t="s">
         <v>31</v>
-      </c>
-      <c r="E7" s="96" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="96" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="96" t="s">
-        <v>29</v>
       </c>
       <c r="H7" s="97">
         <v>3728.0</v>
@@ -44033,19 +44060,19 @@
         <v>45526.0</v>
       </c>
       <c r="B8" s="94" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="94" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="94" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="96" t="s">
-        <v>34</v>
-      </c>
       <c r="E8" s="96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" s="96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H8" s="97">
         <v>3728.0</v>
@@ -44056,7 +44083,7 @@
         <v>45526.0</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I9" s="97">
         <v>12.0</v>
@@ -44073,22 +44100,22 @@
         <v>45526.0</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="94" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" s="96" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E10" s="96" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F10" s="96" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G10" s="96" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H10" s="97">
         <v>3728.0</v>
@@ -44099,22 +44126,22 @@
         <v>45526.0</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="94" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="96" t="s">
+      <c r="G11" s="96" t="s">
         <v>31</v>
-      </c>
-      <c r="E11" s="96" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="96" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="96" t="s">
-        <v>29</v>
       </c>
       <c r="H11" s="97">
         <v>3728.0</v>
@@ -44125,19 +44152,19 @@
         <v>45526.0</v>
       </c>
       <c r="B12" s="94" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="94" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="94" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="96" t="s">
-        <v>34</v>
-      </c>
       <c r="E12" s="96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G12" s="96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H12" s="97">
         <v>3728.0</v>
@@ -44148,7 +44175,7 @@
         <v>45526.0</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I13" s="97">
         <v>12.0</v>
@@ -44165,7 +44192,7 @@
         <v>45532.0</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -44173,7 +44200,7 @@
         <v>45533.0</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -44181,7 +44208,7 @@
         <v>45534.0</v>
       </c>
       <c r="B16" s="94" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -44189,7 +44216,7 @@
         <v>45535.0</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -44223,7 +44250,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="98" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -44427,7 +44454,7 @@
       <c r="Y19" s="100"/>
       <c r="Z19" s="100"/>
       <c r="AA19" s="94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AB19" s="94">
         <v>-11.0</v>
@@ -44752,7 +44779,7 @@
       <c r="Y30" s="100"/>
       <c r="Z30" s="100"/>
       <c r="AA30" s="94" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AB30" s="94">
         <v>-8.0</v>
@@ -44873,7 +44900,7 @@
       <c r="Y34" s="100"/>
       <c r="Z34" s="100"/>
       <c r="AA34" s="94" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AB34" s="94">
         <v>0.0</v>
@@ -44992,7 +45019,7 @@
       <c r="Y38" s="100"/>
       <c r="Z38" s="100"/>
       <c r="AA38" s="94" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AB38" s="94">
         <v>-12.0</v>
@@ -45026,7 +45053,7 @@
       <c r="Y39" s="100"/>
       <c r="Z39" s="100"/>
       <c r="AA39" s="94" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB39" s="94">
         <v>0.0</v>
@@ -45118,7 +45145,7 @@
       <c r="Y42" s="100"/>
       <c r="Z42" s="100"/>
       <c r="AA42" s="94" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AB42" s="94">
         <v>6.0</v>
@@ -45297,7 +45324,7 @@
       <c r="Y48" s="100"/>
       <c r="Z48" s="100"/>
       <c r="AA48" s="94" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AB48" s="94">
         <v>-13.0</v>
@@ -45418,7 +45445,7 @@
       <c r="Y52" s="100"/>
       <c r="Z52" s="100"/>
       <c r="AA52" s="94" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB52" s="94">
         <v>5.0</v>
@@ -45626,7 +45653,7 @@
       <c r="Y59" s="100"/>
       <c r="Z59" s="100"/>
       <c r="AA59" s="94" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AB59" s="94">
         <v>-9.0</v>
@@ -45747,7 +45774,7 @@
       <c r="Y63" s="100"/>
       <c r="Z63" s="100"/>
       <c r="AA63" s="94" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AB63" s="94">
         <v>-19.0</v>
@@ -45955,7 +45982,7 @@
       <c r="Y70" s="100"/>
       <c r="Z70" s="100"/>
       <c r="AA70" s="94" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB70" s="94">
         <v>-14.0</v>
@@ -46424,7 +46451,7 @@
       <c r="Y86" s="100"/>
       <c r="Z86" s="100"/>
       <c r="AA86" s="94" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB86" s="94">
         <v>-21.0</v>
@@ -46458,7 +46485,7 @@
       <c r="Y87" s="100"/>
       <c r="Z87" s="100"/>
       <c r="AA87" s="94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AB87" s="94">
         <v>-7.0</v>
@@ -46492,7 +46519,7 @@
       <c r="Y88" s="100"/>
       <c r="Z88" s="100"/>
       <c r="AA88" s="94" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AB88" s="94">
         <v>-10.0</v>
@@ -46526,7 +46553,7 @@
       <c r="Y89" s="100"/>
       <c r="Z89" s="100"/>
       <c r="AA89" s="94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AB89" s="94">
         <v>-6.0</v>
@@ -46619,7 +46646,7 @@
       <c r="Y92" s="100"/>
       <c r="Z92" s="100"/>
       <c r="AA92" s="94" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB92" s="94">
         <v>-17.0</v>
@@ -46885,7 +46912,7 @@
       <c r="Y101" s="100"/>
       <c r="Z101" s="100"/>
       <c r="AA101" s="94" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AB101" s="94">
         <v>-6.0</v>
@@ -46919,7 +46946,7 @@
       <c r="Y102" s="100"/>
       <c r="Z102" s="100"/>
       <c r="AA102" s="94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AB102" s="94">
         <v>1.0</v>
@@ -47011,7 +47038,7 @@
       <c r="Y105" s="100"/>
       <c r="Z105" s="100"/>
       <c r="AA105" s="94" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AB105" s="94">
         <v>-2.0</v>
@@ -47074,7 +47101,7 @@
       <c r="Y107" s="100"/>
       <c r="Z107" s="100"/>
       <c r="AA107" s="94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AB107" s="94">
         <v>-12.0</v>
@@ -47166,7 +47193,7 @@
       <c r="Y110" s="100"/>
       <c r="Z110" s="100"/>
       <c r="AA110" s="94" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AB110" s="94">
         <v>-14.0</v>
@@ -47200,7 +47227,7 @@
       <c r="Y111" s="100"/>
       <c r="Z111" s="100"/>
       <c r="AA111" s="94" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AB111" s="94">
         <v>-6.0</v>
@@ -47234,7 +47261,7 @@
       <c r="Y112" s="100"/>
       <c r="Z112" s="100"/>
       <c r="AA112" s="94" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB112" s="94">
         <v>-11.0</v>
@@ -47297,7 +47324,7 @@
       <c r="Y114" s="100"/>
       <c r="Z114" s="100"/>
       <c r="AA114" s="94" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB114" s="94">
         <v>-1.0</v>
@@ -47389,7 +47416,7 @@
       <c r="Y117" s="100"/>
       <c r="Z117" s="100"/>
       <c r="AA117" s="94" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB117" s="94">
         <v>12.0</v>
@@ -47452,7 +47479,7 @@
       <c r="Y119" s="100"/>
       <c r="Z119" s="100"/>
       <c r="AA119" s="94" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AB119" s="94">
         <v>-17.0</v>
@@ -47573,7 +47600,7 @@
       <c r="Y123" s="100"/>
       <c r="Z123" s="100"/>
       <c r="AA123" s="94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB123" s="94">
         <v>-15.0</v>
@@ -47724,7 +47751,7 @@
       <c r="Y128" s="100"/>
       <c r="Z128" s="100"/>
       <c r="AA128" s="94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AB128" s="94">
         <v>-11.0</v>
@@ -48109,7 +48136,7 @@
       <c r="Y141" s="100"/>
       <c r="Z141" s="100"/>
       <c r="AA141" s="94" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AB141" s="94">
         <v>-10.0</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Report Vyroba.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Výroba/Report Vyroba.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="70">
   <si>
     <t>Výroba</t>
   </si>
@@ -78,6 +78,12 @@
     <t>Kursheva Diana</t>
   </si>
   <si>
+    <t>Hřebík Martin</t>
+  </si>
+  <si>
+    <t>Lažek Jaroslav</t>
+  </si>
+  <si>
     <t>Manažeři</t>
   </si>
   <si>
@@ -118,9 +124,6 @@
   </si>
   <si>
     <t>11:00</t>
-  </si>
-  <si>
-    <t>Hřebík Martin</t>
   </si>
   <si>
     <t>05:00</t>
@@ -1387,7 +1390,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46173.0</v>
+        <v>46176.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -1416,7 +1419,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Neděle</v>
+        <v>Středa</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1707,7 +1710,7 @@
   </conditionalFormatting>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="B14:B20">
-      <formula1>"Sova Martin,Paziak Viktoriia,Stepanenko Solomiia,Kursheva Diana,Lažek Jaroslav,Chlubna Tomáš,Hřebík Martin"</formula1>
+      <formula1>"Sova Martin,Paziak Viktoriia,Ahurieva Viktoriia,Stepanenko Solomiia,Kursheva Diana,Lažek Jaroslav,Chlubna Tomáš,Hřebík Martin"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
@@ -1737,13 +1740,13 @@
         <v>Výroba</v>
       </c>
       <c r="C1" s="62">
-        <v>46101.0</v>
+        <v>46143.0</v>
       </c>
       <c r="D1" s="63" t="s">
         <v>14</v>
       </c>
       <c r="E1" s="62">
-        <v>46101.0</v>
+        <v>46173.0</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>2</v>
@@ -1759,7 +1762,7 @@
       <c r="D2" s="12"/>
       <c r="E2" s="13"/>
       <c r="F2" s="65">
-        <v>41620.0</v>
+        <v>1224796.0</v>
       </c>
       <c r="H2" s="16"/>
     </row>
@@ -1772,7 +1775,7 @@
       <c r="C3" s="10"/>
       <c r="D3" s="67" t="str">
         <f>CHOOSE(WEEKDAY(E1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Pátek</v>
+        <v>Neděle</v>
       </c>
       <c r="E3" s="5"/>
       <c r="H3" s="16"/>
@@ -1876,10 +1879,10 @@
         <v>17</v>
       </c>
       <c r="C10" s="81">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="D10" s="82">
-        <v>8.0</v>
+        <v>118.0</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
@@ -1888,10 +1891,10 @@
         <v>18</v>
       </c>
       <c r="C11" s="81">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="D11" s="82">
-        <v>8.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
@@ -1900,23 +1903,35 @@
         <v>19</v>
       </c>
       <c r="C12" s="81">
-        <v>1.0</v>
+        <v>18.0</v>
       </c>
       <c r="D12" s="82">
-        <v>8.0</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="71"/>
-      <c r="B13" s="80"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="83"/>
+      <c r="B13" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="81">
+        <v>11.0</v>
+      </c>
+      <c r="D13" s="83">
+        <v>116.0</v>
+      </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71"/>
-      <c r="B14" s="80"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="83"/>
+      <c r="B14" s="80" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="83">
+        <v>13.0</v>
+      </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="71"/>
@@ -2123,10 +2138,10 @@
     </row>
     <row r="4">
       <c r="A4" s="88" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -2223,8 +2238,8 @@
       <c r="T5" s="84"/>
       <c r="U5" s="84"/>
       <c r="V5" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),223.0)</f>
-        <v>223</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),256.5)</f>
+        <v>256.5</v>
       </c>
       <c r="W5" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2289,8 +2304,8 @@
       <c r="T6" s="84"/>
       <c r="U6" s="84"/>
       <c r="V6" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),177.5)</f>
-        <v>177.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),208.0)</f>
+        <v>208</v>
       </c>
       <c r="W6" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2349,8 +2364,8 @@
       <c r="T7" s="84"/>
       <c r="U7" s="84"/>
       <c r="V7" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.5)</f>
-        <v>110.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),119.0)</f>
+        <v>119</v>
       </c>
       <c r="W7" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2378,7 +2393,7 @@
       </c>
       <c r="B8" s="89" t="str">
         <f>IF(OR(E8=Report!$B$1, F8=Report!$B$1, G8=Report!$B$1, H8=Report!$B$1), D8, "")</f>
-        <v/>
+        <v>Ahurieva Viktoriia</v>
       </c>
       <c r="C8" s="84" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -2397,8 +2412,8 @@
         <v>Malešice</v>
       </c>
       <c r="G8" s="84" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Zličín")</f>
-        <v>Zličín</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Výroba")</f>
+        <v>Výroba</v>
       </c>
       <c r="H8" s="84" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
@@ -2418,8 +2433,8 @@
       <c r="T8" s="84"/>
       <c r="U8" s="84"/>
       <c r="V8" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),190.0)</f>
-        <v>190</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),206.5)</f>
+        <v>206.5</v>
       </c>
       <c r="W8" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2481,8 +2496,8 @@
       <c r="T9" s="84"/>
       <c r="U9" s="84"/>
       <c r="V9" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),173.5)</f>
-        <v>173.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),193.5)</f>
+        <v>193.5</v>
       </c>
       <c r="W9" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2550,8 +2565,8 @@
       <c r="T10" s="84"/>
       <c r="U10" s="84"/>
       <c r="V10" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),160.0)</f>
-        <v>160</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),178.5)</f>
+        <v>178.5</v>
       </c>
       <c r="W10" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -2610,12 +2625,12 @@
       <c r="T11" s="84"/>
       <c r="U11" s="84"/>
       <c r="V11" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.5)</f>
-        <v>110.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.5)</f>
+        <v>117.5</v>
       </c>
       <c r="W11" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20494.647)</f>
-        <v>20494.647</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21630.145)</f>
+        <v>21630.145</v>
       </c>
       <c r="X11" s="84"/>
       <c r="Y11" s="84"/>
@@ -2730,8 +2745,8 @@
       <c r="T13" s="84"/>
       <c r="U13" s="84"/>
       <c r="V13" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
-        <v>110</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.5)</f>
+        <v>148.5</v>
       </c>
       <c r="W13" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2796,12 +2811,12 @@
       <c r="T14" s="84"/>
       <c r="U14" s="84"/>
       <c r="V14" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.5)</f>
-        <v>54.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63.5)</f>
+        <v>63.5</v>
       </c>
       <c r="W14" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9009.286)</f>
-        <v>9009.286</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10497.058)</f>
+        <v>10497.058</v>
       </c>
       <c r="X14" s="84"/>
       <c r="Y14" s="84"/>
@@ -2859,8 +2874,8 @@
       <c r="T15" s="84"/>
       <c r="U15" s="84"/>
       <c r="V15" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),169.5)</f>
-        <v>169.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),183.0)</f>
+        <v>183</v>
       </c>
       <c r="W15" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -2922,8 +2937,8 @@
       <c r="T16" s="84"/>
       <c r="U16" s="84"/>
       <c r="V16" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.0)</f>
-        <v>153</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),159.0)</f>
+        <v>159</v>
       </c>
       <c r="W16" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40004.0)</f>
@@ -3102,12 +3117,12 @@
       <c r="T19" s="84"/>
       <c r="U19" s="84"/>
       <c r="V19" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),153.5)</f>
-        <v>153.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),184.0)</f>
+        <v>184</v>
       </c>
       <c r="W19" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31300.595)</f>
-        <v>31300.595</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37009.28)</f>
+        <v>37009.28</v>
       </c>
       <c r="X19" s="84"/>
       <c r="Y19" s="84"/>
@@ -3162,12 +3177,12 @@
       <c r="T20" s="84"/>
       <c r="U20" s="84"/>
       <c r="V20" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.5)</f>
-        <v>54.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.5)</f>
+        <v>59.5</v>
       </c>
       <c r="W20" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9635.6)</f>
-        <v>9635.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10519.6)</f>
+        <v>10519.6</v>
       </c>
       <c r="X20" s="84"/>
       <c r="Y20" s="84"/>
@@ -3231,8 +3246,8 @@
       <c r="T21" s="84"/>
       <c r="U21" s="84"/>
       <c r="V21" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),156.0)</f>
-        <v>156</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),185.0)</f>
+        <v>185</v>
       </c>
       <c r="W21" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3291,8 +3306,8 @@
       <c r="T22" s="84"/>
       <c r="U22" s="84"/>
       <c r="V22" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),255.5)</f>
-        <v>255.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),273.5)</f>
+        <v>273.5</v>
       </c>
       <c r="W22" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50001.08)</f>
@@ -3414,12 +3429,12 @@
       <c r="T24" s="84"/>
       <c r="U24" s="84"/>
       <c r="V24" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),176.0)</f>
-        <v>176</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201.5)</f>
+        <v>201.5</v>
       </c>
       <c r="W24" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28406.8)</f>
-        <v>28406.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32150.199999999997)</f>
+        <v>32150.2</v>
       </c>
       <c r="X24" s="84"/>
       <c r="Y24" s="84"/>
@@ -3588,12 +3603,12 @@
       <c r="T27" s="84"/>
       <c r="U27" s="84"/>
       <c r="V27" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),59.5)</f>
-        <v>59.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),71.5)</f>
+        <v>71.5</v>
       </c>
       <c r="W27" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11255.972)</f>
-        <v>11255.972</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13526.084)</f>
+        <v>13526.084</v>
       </c>
       <c r="X27" s="84"/>
       <c r="Y27" s="84"/>
@@ -3657,12 +3672,12 @@
       <c r="T28" s="84"/>
       <c r="U28" s="84"/>
       <c r="V28" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),166.5)</f>
-        <v>166.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),192.5)</f>
+        <v>192.5</v>
       </c>
       <c r="W28" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27012.2)</f>
-        <v>27012.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30829.0)</f>
+        <v>30829</v>
       </c>
       <c r="X28" s="84"/>
       <c r="Y28" s="84"/>
@@ -3777,12 +3792,12 @@
       <c r="T30" s="84"/>
       <c r="U30" s="84"/>
       <c r="V30" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),169.5)</f>
-        <v>169.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),185.0)</f>
+        <v>185</v>
       </c>
       <c r="W30" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25835.231)</f>
-        <v>25835.231</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27962.73)</f>
+        <v>27962.73</v>
       </c>
       <c r="X30" s="84"/>
       <c r="Y30" s="84"/>
@@ -3843,12 +3858,12 @@
       <c r="T31" s="84"/>
       <c r="U31" s="84"/>
       <c r="V31" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.5)</f>
-        <v>117.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),131.5)</f>
+        <v>131.5</v>
       </c>
       <c r="W31" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17490.385000000002)</f>
-        <v>17490.385</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19268.133)</f>
+        <v>19268.133</v>
       </c>
       <c r="X31" s="84"/>
       <c r="Y31" s="84"/>
@@ -4086,12 +4101,12 @@
       <c r="T35" s="84"/>
       <c r="U35" s="84"/>
       <c r="V35" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),134.0)</f>
-        <v>134</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),142.5)</f>
+        <v>142.5</v>
       </c>
       <c r="W35" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20962.572)</f>
-        <v>20962.572</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22129.265)</f>
+        <v>22129.265</v>
       </c>
       <c r="X35" s="84"/>
       <c r="Y35" s="84"/>
@@ -4269,12 +4284,12 @@
       <c r="T38" s="84"/>
       <c r="U38" s="84"/>
       <c r="V38" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),154.5)</f>
-        <v>154.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.5)</f>
+        <v>182.5</v>
       </c>
       <c r="W38" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23776.361)</f>
-        <v>23776.361</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27619.585)</f>
+        <v>27619.585</v>
       </c>
       <c r="X38" s="84"/>
       <c r="Y38" s="84"/>
@@ -4338,12 +4353,12 @@
       <c r="T39" s="84"/>
       <c r="U39" s="84"/>
       <c r="V39" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),164.0)</f>
-        <v>164</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),188.5)</f>
+        <v>188.5</v>
       </c>
       <c r="W39" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25080.311999999998)</f>
-        <v>25080.312</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28443.133)</f>
+        <v>28443.133</v>
       </c>
       <c r="X39" s="84"/>
       <c r="Y39" s="84"/>
@@ -4398,12 +4413,12 @@
       <c r="T40" s="84"/>
       <c r="U40" s="84"/>
       <c r="V40" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
-        <v>23</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
+        <v>40</v>
       </c>
       <c r="W40" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3802.084)</f>
-        <v>3802.084</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6612.32)</f>
+        <v>6612.32</v>
       </c>
       <c r="X40" s="84"/>
       <c r="Y40" s="84"/>
@@ -4458,12 +4473,12 @@
       <c r="T41" s="84"/>
       <c r="U41" s="84"/>
       <c r="V41" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),150.5)</f>
-        <v>150.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),165.5)</f>
+        <v>165.5</v>
       </c>
       <c r="W41" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23227.328999999998)</f>
-        <v>23227.329</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25286.199)</f>
+        <v>25286.199</v>
       </c>
       <c r="X41" s="84"/>
       <c r="Y41" s="84"/>
@@ -5379,12 +5394,12 @@
       <c r="T60" s="84"/>
       <c r="U60" s="84"/>
       <c r="V60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3884.0)</f>
-        <v>3884</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4354.0)</f>
+        <v>4354</v>
       </c>
       <c r="W60" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),909421.29)</f>
-        <v>909421.29</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),945614.6479999999)</f>
+        <v>945614.648</v>
       </c>
       <c r="X60" s="84"/>
       <c r="Y60" s="84"/>
@@ -6066,12 +6081,12 @@
       <c r="T75" s="84"/>
       <c r="U75" s="84"/>
       <c r="V75" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),92.5)</f>
-        <v>92.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),106.5)</f>
+        <v>106.5</v>
       </c>
       <c r="W75" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13875.0)</f>
-        <v>13875</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15975.0)</f>
+        <v>15975</v>
       </c>
       <c r="X75" s="84"/>
       <c r="Y75" s="84"/>
@@ -6123,12 +6138,12 @@
       <c r="T76" s="84"/>
       <c r="U76" s="84"/>
       <c r="V76" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),131.0)</f>
-        <v>131</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),138.0)</f>
+        <v>138</v>
       </c>
       <c r="W76" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21800.8)</f>
-        <v>21800.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22828.4)</f>
+        <v>22828.4</v>
       </c>
       <c r="X76" s="84"/>
       <c r="Y76" s="84"/>
@@ -6363,12 +6378,12 @@
       <c r="T80" s="84"/>
       <c r="U80" s="84"/>
       <c r="V80" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),82.5)</f>
-        <v>82.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
+        <v>98</v>
       </c>
       <c r="W80" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13637.91)</f>
-        <v>13637.91</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16021.284000000001)</f>
+        <v>16021.284</v>
       </c>
       <c r="X80" s="84"/>
       <c r="Y80" s="84"/>
@@ -6423,12 +6438,12 @@
       <c r="T81" s="84"/>
       <c r="U81" s="84"/>
       <c r="V81" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),149.5)</f>
-        <v>149.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),168.0)</f>
+        <v>168</v>
       </c>
       <c r="W81" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21553.808999999997)</f>
-        <v>21553.809</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23902.976000000002)</f>
+        <v>23902.976</v>
       </c>
       <c r="X81" s="84"/>
       <c r="Y81" s="84"/>
@@ -6597,12 +6612,12 @@
       <c r="T84" s="84"/>
       <c r="U84" s="84"/>
       <c r="V84" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.5)</f>
-        <v>51.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.5)</f>
+        <v>58.5</v>
       </c>
       <c r="W84" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8513.362000000001)</f>
-        <v>8513.362</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9670.518)</f>
+        <v>9670.518</v>
       </c>
       <c r="X84" s="84"/>
       <c r="Y84" s="84"/>
@@ -6654,12 +6669,12 @@
       <c r="T85" s="84"/>
       <c r="U85" s="84"/>
       <c r="V85" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.0)</f>
-        <v>40</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.0)</f>
+        <v>44</v>
       </c>
       <c r="W85" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6000.0)</f>
-        <v>6000</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6600.0)</f>
+        <v>6600</v>
       </c>
       <c r="X85" s="84"/>
       <c r="Y85" s="84"/>
@@ -6894,12 +6909,12 @@
       <c r="T89" s="84"/>
       <c r="U89" s="84"/>
       <c r="V89" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
-        <v>76</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.0)</f>
+        <v>78</v>
       </c>
       <c r="W89" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12920.0)</f>
-        <v>12920</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13260.0)</f>
+        <v>13260</v>
       </c>
       <c r="X89" s="84"/>
       <c r="Y89" s="84"/>
@@ -6954,12 +6969,12 @@
       <c r="T90" s="84"/>
       <c r="U90" s="84"/>
       <c r="V90" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
-        <v>117</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),141.0)</f>
+        <v>141</v>
       </c>
       <c r="W90" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18720.0)</f>
-        <v>18720</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22560.0)</f>
+        <v>22560</v>
       </c>
       <c r="X90" s="84"/>
       <c r="Y90" s="84"/>
@@ -7119,12 +7134,12 @@
       <c r="T93" s="84"/>
       <c r="U93" s="84"/>
       <c r="V93" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),194.5)</f>
-        <v>194.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),228.0)</f>
+        <v>228</v>
       </c>
       <c r="W93" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29266.680999999997)</f>
-        <v>29266.681</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33864.824)</f>
+        <v>33864.824</v>
       </c>
       <c r="X93" s="84"/>
       <c r="Y93" s="84"/>
@@ -7182,12 +7197,12 @@
       <c r="T94" s="84"/>
       <c r="U94" s="84"/>
       <c r="V94" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),242.0)</f>
-        <v>242</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),281.0)</f>
+        <v>281</v>
       </c>
       <c r="W94" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35786.436)</f>
-        <v>35786.436</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),41139.49800000001)</f>
+        <v>41139.498</v>
       </c>
       <c r="X94" s="84"/>
       <c r="Y94" s="84"/>
@@ -7299,8 +7314,8 @@
       <c r="T96" s="84"/>
       <c r="U96" s="84"/>
       <c r="V96" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),130.0)</f>
-        <v>130</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),142.0)</f>
+        <v>142</v>
       </c>
       <c r="W96" s="87">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44995.2)</f>
@@ -7356,12 +7371,12 @@
       <c r="T97" s="84"/>
       <c r="U97" s="84"/>
       <c r="V97" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
-        <v>70</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),75.5)</f>
+        <v>75.5</v>
       </c>
       <c r="W97" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11571.56)</f>
-        <v>11571.56</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12480.754)</f>
+        <v>12480.754</v>
       </c>
       <c r="X97" s="84"/>
       <c r="Y97" s="84"/>
@@ -7812,12 +7827,12 @@
       <c r="T105" s="84"/>
       <c r="U105" s="84"/>
       <c r="V105" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
-        <v>98</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),107.0)</f>
+        <v>107</v>
       </c>
       <c r="W105" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14987.336)</f>
-        <v>14987.336</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16157.074)</f>
+        <v>16157.074</v>
       </c>
       <c r="X105" s="84"/>
       <c r="Y105" s="84"/>
@@ -7920,12 +7935,12 @@
       <c r="T107" s="84"/>
       <c r="U107" s="84"/>
       <c r="V107" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),198.0)</f>
-        <v>198</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),215.0)</f>
+        <v>215</v>
       </c>
       <c r="W107" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27720.0)</f>
-        <v>27720</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30100.0)</f>
+        <v>30100</v>
       </c>
       <c r="X107" s="84"/>
       <c r="Y107" s="84"/>
@@ -8208,12 +8223,12 @@
       <c r="T112" s="84"/>
       <c r="U112" s="84"/>
       <c r="V112" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.5)</f>
-        <v>8.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.5)</f>
+        <v>17.5</v>
       </c>
       <c r="W112" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1202.24)</f>
-        <v>1202.24</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2475.2)</f>
+        <v>2475.2</v>
       </c>
       <c r="X112" s="84"/>
       <c r="Y112" s="84"/>
@@ -8382,12 +8397,12 @@
       <c r="T115" s="84"/>
       <c r="U115" s="84"/>
       <c r="V115" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.5)</f>
-        <v>44.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),58.0)</f>
+        <v>58</v>
       </c>
       <c r="W115" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7356.206)</f>
-        <v>7356.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9587.864)</f>
+        <v>9587.864</v>
       </c>
       <c r="X115" s="84"/>
       <c r="Y115" s="84"/>
@@ -8496,12 +8511,12 @@
       <c r="T117" s="84"/>
       <c r="U117" s="84"/>
       <c r="V117" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),182.0)</f>
-        <v>182</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),218.0)</f>
+        <v>218</v>
       </c>
       <c r="W117" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27550.956)</f>
-        <v>27550.956</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32492.244)</f>
+        <v>32492.244</v>
       </c>
       <c r="X117" s="84"/>
       <c r="Y117" s="84"/>
@@ -8604,12 +8619,12 @@
       <c r="T119" s="84"/>
       <c r="U119" s="84"/>
       <c r="V119" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.0)</f>
-        <v>32</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
+        <v>48</v>
       </c>
       <c r="W119" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4526.08)</f>
-        <v>4526.08</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6789.12)</f>
+        <v>6789.12</v>
       </c>
       <c r="X119" s="84"/>
       <c r="Y119" s="84"/>
@@ -8988,12 +9003,12 @@
       <c r="T126" s="84"/>
       <c r="U126" s="84"/>
       <c r="V126" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),65.5)</f>
-        <v>65.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),81.5)</f>
+        <v>81.5</v>
       </c>
       <c r="W126" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10017.046)</f>
-        <v>10017.046</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12463.958)</f>
+        <v>12463.958</v>
       </c>
       <c r="X126" s="84"/>
       <c r="Y126" s="84"/>
@@ -9045,12 +9060,12 @@
       <c r="T127" s="84"/>
       <c r="U127" s="84"/>
       <c r="V127" s="90">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
+        <v>42</v>
       </c>
       <c r="W127" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3230.0)</f>
-        <v>3230</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7140.0)</f>
+        <v>7140</v>
       </c>
       <c r="X127" s="84"/>
       <c r="Y127" s="84"/>
@@ -9077,8 +9092,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D128" s="84"/>
-      <c r="E128" s="84"/>
+      <c r="D128" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Weindling Josef")</f>
+        <v>Weindling Josef</v>
+      </c>
+      <c r="E128" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
+        <v>Libuš</v>
+      </c>
       <c r="F128" s="84"/>
       <c r="G128" s="84"/>
       <c r="H128" s="84"/>
@@ -9125,8 +9146,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D129" s="84"/>
-      <c r="E129" s="84"/>
+      <c r="D129" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fux Vojtěch")</f>
+        <v>Fux Vojtěch</v>
+      </c>
+      <c r="E129" s="84" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
+        <v>Chodov</v>
+      </c>
       <c r="F129" s="84"/>
       <c r="G129" s="84"/>
       <c r="H129" s="84"/>
@@ -12486,12 +12513,12 @@
       <c r="T196" s="84"/>
       <c r="U196" s="84"/>
       <c r="V196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2504.5)</f>
-        <v>2504.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2826.0)</f>
+        <v>2826</v>
       </c>
       <c r="W196" s="87">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),437898.78799999994)</f>
-        <v>437898.788</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),483172.0800000001)</f>
+        <v>483172.08</v>
       </c>
       <c r="X196" s="84"/>
       <c r="Y196" s="84"/>
@@ -43881,7 +43908,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="94" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C1" s="94" t="s">
         <v>4</v>
@@ -43893,16 +43920,16 @@
         <v>8</v>
       </c>
       <c r="F1" s="94" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G1" s="94" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="94" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I1" s="94" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J1" s="94" t="s">
         <v>12</v>
@@ -43916,22 +43943,22 @@
         <v>45528.0</v>
       </c>
       <c r="B2" s="94" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2" s="94" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" s="96" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2" s="96" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F2" s="96" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2" s="96" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H2" s="97">
         <v>3728.0</v>
@@ -43942,22 +43969,22 @@
         <v>45528.0</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" s="94" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="96" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="96" t="s">
+      <c r="G3" s="96" t="s">
         <v>33</v>
-      </c>
-      <c r="F3" s="96" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="96" t="s">
-        <v>31</v>
       </c>
       <c r="H3" s="97">
         <v>3728.0</v>
@@ -43968,19 +43995,19 @@
         <v>45528.0</v>
       </c>
       <c r="B4" s="94" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="96" t="s">
-        <v>32</v>
-      </c>
       <c r="G4" s="96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" s="97">
         <v>3728.0</v>
@@ -43991,7 +44018,7 @@
         <v>45528.0</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I5" s="97">
         <v>12.0</v>
@@ -44008,22 +44035,22 @@
         <v>45526.0</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" s="94" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="96" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E6" s="96" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6" s="96" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6" s="96" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H6" s="97">
         <v>3728.0</v>
@@ -44034,22 +44061,22 @@
         <v>45526.0</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" s="94" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="96" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="96" t="s">
+      <c r="G7" s="96" t="s">
         <v>33</v>
-      </c>
-      <c r="F7" s="96" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="96" t="s">
-        <v>31</v>
       </c>
       <c r="H7" s="97">
         <v>3728.0</v>
@@ -44060,19 +44087,19 @@
         <v>45526.0</v>
       </c>
       <c r="B8" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="E8" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="96" t="s">
-        <v>32</v>
-      </c>
       <c r="G8" s="96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H8" s="97">
         <v>3728.0</v>
@@ -44083,7 +44110,7 @@
         <v>45526.0</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I9" s="97">
         <v>12.0</v>
@@ -44100,22 +44127,22 @@
         <v>45526.0</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="94" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D10" s="96" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E10" s="96" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F10" s="96" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G10" s="96" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H10" s="97">
         <v>3728.0</v>
@@ -44126,22 +44153,22 @@
         <v>45526.0</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" s="94" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="96" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="96" t="s">
+      <c r="G11" s="96" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" s="96" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="96" t="s">
-        <v>31</v>
       </c>
       <c r="H11" s="97">
         <v>3728.0</v>
@@ -44152,19 +44179,19 @@
         <v>45526.0</v>
       </c>
       <c r="B12" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="94" t="s">
+      <c r="E12" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="96" t="s">
-        <v>32</v>
-      </c>
       <c r="G12" s="96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H12" s="97">
         <v>3728.0</v>
@@ -44175,7 +44202,7 @@
         <v>45526.0</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I13" s="97">
         <v>12.0</v>
@@ -44192,7 +44219,7 @@
         <v>45532.0</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -44200,7 +44227,7 @@
         <v>45533.0</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
@@ -44208,7 +44235,7 @@
         <v>45534.0</v>
       </c>
       <c r="B16" s="94" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -44216,7 +44243,7 @@
         <v>45535.0</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -44250,7 +44277,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="98" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -44454,7 +44481,7 @@
       <c r="Y19" s="100"/>
       <c r="Z19" s="100"/>
       <c r="AA19" s="94" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AB19" s="94">
         <v>-11.0</v>
@@ -44779,7 +44806,7 @@
       <c r="Y30" s="100"/>
       <c r="Z30" s="100"/>
       <c r="AA30" s="94" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AB30" s="94">
         <v>-8.0</v>
@@ -44900,7 +44927,7 @@
       <c r="Y34" s="100"/>
       <c r="Z34" s="100"/>
       <c r="AA34" s="94" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AB34" s="94">
         <v>0.0</v>
@@ -45019,7 +45046,7 @@
       <c r="Y38" s="100"/>
       <c r="Z38" s="100"/>
       <c r="AA38" s="94" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB38" s="94">
         <v>-12.0</v>
@@ -45053,7 +45080,7 @@
       <c r="Y39" s="100"/>
       <c r="Z39" s="100"/>
       <c r="AA39" s="94" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AB39" s="94">
         <v>0.0</v>
@@ -45145,7 +45172,7 @@
       <c r="Y42" s="100"/>
       <c r="Z42" s="100"/>
       <c r="AA42" s="94" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AB42" s="94">
         <v>6.0</v>
@@ -45324,7 +45351,7 @@
       <c r="Y48" s="100"/>
       <c r="Z48" s="100"/>
       <c r="AA48" s="94" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB48" s="94">
         <v>-13.0</v>
@@ -45445,7 +45472,7 @@
       <c r="Y52" s="100"/>
       <c r="Z52" s="100"/>
       <c r="AA52" s="94" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AB52" s="94">
         <v>5.0</v>
@@ -45653,7 +45680,7 @@
       <c r="Y59" s="100"/>
       <c r="Z59" s="100"/>
       <c r="AA59" s="94" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AB59" s="94">
         <v>-9.0</v>
@@ -45774,7 +45801,7 @@
       <c r="Y63" s="100"/>
       <c r="Z63" s="100"/>
       <c r="AA63" s="94" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB63" s="94">
         <v>-19.0</v>
@@ -45982,7 +46009,7 @@
       <c r="Y70" s="100"/>
       <c r="Z70" s="100"/>
       <c r="AA70" s="94" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB70" s="94">
         <v>-14.0</v>
@@ -46451,7 +46478,7 @@
       <c r="Y86" s="100"/>
       <c r="Z86" s="100"/>
       <c r="AA86" s="94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AB86" s="94">
         <v>-21.0</v>
@@ -46485,7 +46512,7 @@
       <c r="Y87" s="100"/>
       <c r="Z87" s="100"/>
       <c r="AA87" s="94" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AB87" s="94">
         <v>-7.0</v>
@@ -46519,7 +46546,7 @@
       <c r="Y88" s="100"/>
       <c r="Z88" s="100"/>
       <c r="AA88" s="94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AB88" s="94">
         <v>-10.0</v>
@@ -46553,7 +46580,7 @@
       <c r="Y89" s="100"/>
       <c r="Z89" s="100"/>
       <c r="AA89" s="94" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB89" s="94">
         <v>-6.0</v>
@@ -46646,7 +46673,7 @@
       <c r="Y92" s="100"/>
       <c r="Z92" s="100"/>
       <c r="AA92" s="94" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AB92" s="94">
         <v>-17.0</v>
@@ -46912,7 +46939,7 @@
       <c r="Y101" s="100"/>
       <c r="Z101" s="100"/>
       <c r="AA101" s="94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AB101" s="94">
         <v>-6.0</v>
@@ -46946,7 +46973,7 @@
       <c r="Y102" s="100"/>
       <c r="Z102" s="100"/>
       <c r="AA102" s="94" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AB102" s="94">
         <v>1.0</v>
@@ -47038,7 +47065,7 @@
       <c r="Y105" s="100"/>
       <c r="Z105" s="100"/>
       <c r="AA105" s="94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AB105" s="94">
         <v>-2.0</v>
@@ -47101,7 +47128,7 @@
       <c r="Y107" s="100"/>
       <c r="Z107" s="100"/>
       <c r="AA107" s="94" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AB107" s="94">
         <v>-12.0</v>
@@ -47193,7 +47220,7 @@
       <c r="Y110" s="100"/>
       <c r="Z110" s="100"/>
       <c r="AA110" s="94" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AB110" s="94">
         <v>-14.0</v>
@@ -47227,7 +47254,7 @@
       <c r="Y111" s="100"/>
       <c r="Z111" s="100"/>
       <c r="AA111" s="94" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB111" s="94">
         <v>-6.0</v>
@@ -47261,7 +47288,7 @@
       <c r="Y112" s="100"/>
       <c r="Z112" s="100"/>
       <c r="AA112" s="94" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB112" s="94">
         <v>-11.0</v>
@@ -47324,7 +47351,7 @@
       <c r="Y114" s="100"/>
       <c r="Z114" s="100"/>
       <c r="AA114" s="94" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB114" s="94">
         <v>-1.0</v>
@@ -47416,7 +47443,7 @@
       <c r="Y117" s="100"/>
       <c r="Z117" s="100"/>
       <c r="AA117" s="94" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AB117" s="94">
         <v>12.0</v>
@@ -47479,7 +47506,7 @@
       <c r="Y119" s="100"/>
       <c r="Z119" s="100"/>
       <c r="AA119" s="94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB119" s="94">
         <v>-17.0</v>
@@ -47600,7 +47627,7 @@
       <c r="Y123" s="100"/>
       <c r="Z123" s="100"/>
       <c r="AA123" s="94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AB123" s="94">
         <v>-15.0</v>
@@ -47751,7 +47778,7 @@
       <c r="Y128" s="100"/>
       <c r="Z128" s="100"/>
       <c r="AA128" s="94" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AB128" s="94">
         <v>-11.0</v>
@@ -48136,7 +48163,7 @@
       <c r="Y141" s="100"/>
       <c r="Z141" s="100"/>
       <c r="AA141" s="94" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB141" s="94">
         <v>-10.0</v>
